--- a/research/traditional_assets/database/data/taiwan/taiwan_trucking.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_trucking.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08826933483635638</v>
+        <v>0.08812879616668366</v>
       </c>
       <c r="C2">
-        <v>93.70008940863471</v>
+        <v>93.03517034350556</v>
       </c>
       <c r="D2">
-        <v>90.08008940863471</v>
+        <v>90.37917034350555</v>
       </c>
       <c r="E2">
-        <v>-14.7</v>
+        <v>-13.736</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9640000000000001</v>
       </c>
       <c r="G2">
         <v>3.62</v>
@@ -1582,28 +1582,28 @@
         <v>2.27</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0484892</v>
       </c>
       <c r="N2">
-        <v>2.27</v>
+        <v>2.2215108</v>
       </c>
       <c r="O2">
-        <v>0.454</v>
+        <v>0.44430216</v>
       </c>
       <c r="P2">
-        <v>1.816</v>
+        <v>1.77720864</v>
       </c>
       <c r="Q2">
-        <v>5.046</v>
+        <v>5.00720864</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08826933483635638</v>
+        <v>0.08861252138048856</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919477</v>
+        <v>0.8344957286098625</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>46.81454839428161</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08812879616668366</v>
+        <v>0.08798825749701095</v>
       </c>
       <c r="C3">
-        <v>93.03517034350556</v>
+        <v>92.37224389144954</v>
       </c>
       <c r="D3">
-        <v>90.37917034350555</v>
+        <v>90.68024389144954</v>
       </c>
       <c r="E3">
-        <v>-13.736</v>
+        <v>-12.772</v>
       </c>
       <c r="F3">
-        <v>0.9640000000000001</v>
+        <v>1.928</v>
       </c>
       <c r="G3">
         <v>3.62</v>
@@ -1664,28 +1664,28 @@
         <v>2.27</v>
       </c>
       <c r="M3">
-        <v>0.0484892</v>
+        <v>0.09697840000000001</v>
       </c>
       <c r="N3">
-        <v>2.2215108</v>
+        <v>2.1730216</v>
       </c>
       <c r="O3">
-        <v>0.44430216</v>
+        <v>0.43460432</v>
       </c>
       <c r="P3">
-        <v>1.77720864</v>
+        <v>1.73841728</v>
       </c>
       <c r="Q3">
-        <v>5.00720864</v>
+        <v>4.968417280000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08861252138048856</v>
+        <v>0.08896271173164383</v>
       </c>
       <c r="T3">
-        <v>0.8344957286098625</v>
+        <v>0.8413215903628366</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>46.81454839428161</v>
+        <v>23.40727419714081</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08798825749701095</v>
+        <v>0.08784771882733824</v>
       </c>
       <c r="C4">
-        <v>92.37224389144954</v>
+        <v>91.71133003256536</v>
       </c>
       <c r="D4">
-        <v>90.68024389144954</v>
+        <v>90.98333003256535</v>
       </c>
       <c r="E4">
-        <v>-12.772</v>
+        <v>-11.808</v>
       </c>
       <c r="F4">
-        <v>1.928</v>
+        <v>2.892</v>
       </c>
       <c r="G4">
         <v>3.62</v>
@@ -1746,28 +1746,28 @@
         <v>2.27</v>
       </c>
       <c r="M4">
-        <v>0.09697840000000001</v>
+        <v>0.1454676</v>
       </c>
       <c r="N4">
-        <v>2.1730216</v>
+        <v>2.1245324</v>
       </c>
       <c r="O4">
-        <v>0.43460432</v>
+        <v>0.42490648</v>
       </c>
       <c r="P4">
-        <v>1.73841728</v>
+        <v>1.69962592</v>
       </c>
       <c r="Q4">
-        <v>4.968417280000001</v>
+        <v>4.92962592</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08896271173164383</v>
+        <v>0.08932012250241056</v>
       </c>
       <c r="T4">
-        <v>0.8413215903628366</v>
+        <v>0.848288191533398</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>23.40727419714081</v>
+        <v>15.60484946476054</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08784771882733824</v>
+        <v>0.08775518015766554</v>
       </c>
       <c r="C5">
-        <v>91.71133003256536</v>
+        <v>90.94800790576163</v>
       </c>
       <c r="D5">
-        <v>90.98333003256535</v>
+        <v>91.18400790576162</v>
       </c>
       <c r="E5">
-        <v>-11.808</v>
+        <v>-10.844</v>
       </c>
       <c r="F5">
-        <v>2.892</v>
+        <v>3.856</v>
       </c>
       <c r="G5">
         <v>3.62</v>
@@ -1828,45 +1828,45 @@
         <v>2.27</v>
       </c>
       <c r="M5">
-        <v>0.1454676</v>
+        <v>0.1997408</v>
       </c>
       <c r="N5">
-        <v>2.1245324</v>
+        <v>2.0702592</v>
       </c>
       <c r="O5">
-        <v>0.42490648</v>
+        <v>0.4140518400000001</v>
       </c>
       <c r="P5">
-        <v>1.69962592</v>
+        <v>1.65620736</v>
       </c>
       <c r="Q5">
-        <v>4.92962592</v>
+        <v>4.88620736</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08932012250241056</v>
+        <v>0.08968497933090161</v>
       </c>
       <c r="T5">
-        <v>0.848288191533398</v>
+        <v>0.855399930228346</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>15.60484946476054</v>
+        <v>11.36472868838014</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08775518015766554</v>
+        <v>0.08769464148799282</v>
       </c>
       <c r="C6">
-        <v>90.94800790576163</v>
+        <v>90.11577078373313</v>
       </c>
       <c r="D6">
-        <v>91.18400790576162</v>
+        <v>91.31577078373311</v>
       </c>
       <c r="E6">
-        <v>-10.844</v>
+        <v>-9.879999999999999</v>
       </c>
       <c r="F6">
-        <v>3.856</v>
+        <v>4.82</v>
       </c>
       <c r="G6">
         <v>3.62</v>
@@ -1910,45 +1910,45 @@
         <v>2.27</v>
       </c>
       <c r="M6">
-        <v>0.1997408</v>
+        <v>0.25787</v>
       </c>
       <c r="N6">
-        <v>2.0702592</v>
+        <v>2.01213</v>
       </c>
       <c r="O6">
-        <v>0.4140518400000001</v>
+        <v>0.402426</v>
       </c>
       <c r="P6">
-        <v>1.65620736</v>
+        <v>1.609704</v>
       </c>
       <c r="Q6">
-        <v>4.88620736</v>
+        <v>4.839704</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08968497933090161</v>
+        <v>0.09005751735578191</v>
       </c>
       <c r="T6">
-        <v>0.855399930228346</v>
+        <v>0.8626613897379244</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>11.36472868838014</v>
+        <v>8.802885174700432</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08769464148799282</v>
+        <v>0.08761810281832011</v>
       </c>
       <c r="C7">
-        <v>90.11577078373313</v>
+        <v>89.31890384680604</v>
       </c>
       <c r="D7">
-        <v>91.31577078373311</v>
+        <v>91.48290384680604</v>
       </c>
       <c r="E7">
-        <v>-9.879999999999999</v>
+        <v>-8.915999999999999</v>
       </c>
       <c r="F7">
-        <v>4.82</v>
+        <v>5.784000000000001</v>
       </c>
       <c r="G7">
         <v>3.62</v>
@@ -1992,45 +1992,45 @@
         <v>2.27</v>
       </c>
       <c r="M7">
-        <v>0.25787</v>
+        <v>0.3140712000000001</v>
       </c>
       <c r="N7">
-        <v>2.01213</v>
+        <v>1.9559288</v>
       </c>
       <c r="O7">
-        <v>0.402426</v>
+        <v>0.39118576</v>
       </c>
       <c r="P7">
-        <v>1.609704</v>
+        <v>1.56474304</v>
       </c>
       <c r="Q7">
-        <v>4.839704</v>
+        <v>4.79474304</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09005751735578191</v>
+        <v>0.09043798172161714</v>
       </c>
       <c r="T7">
-        <v>0.8626613897379244</v>
+        <v>0.8700773483860047</v>
       </c>
       <c r="U7">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y7">
-        <v>8.802885174700432</v>
+        <v>7.227660479534576</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08761810281832011</v>
+        <v>0.08750956414864741</v>
       </c>
       <c r="C8">
-        <v>89.31890384680604</v>
+        <v>88.59296513763948</v>
       </c>
       <c r="D8">
-        <v>91.48290384680604</v>
+        <v>91.72096513763948</v>
       </c>
       <c r="E8">
-        <v>-8.916</v>
+        <v>-7.952</v>
       </c>
       <c r="F8">
-        <v>5.784</v>
+        <v>6.747999999999999</v>
       </c>
       <c r="G8">
         <v>3.62</v>
@@ -2074,28 +2074,28 @@
         <v>2.27</v>
       </c>
       <c r="M8">
-        <v>0.3140712</v>
+        <v>0.3664164</v>
       </c>
       <c r="N8">
-        <v>1.9559288</v>
+        <v>1.9035836</v>
       </c>
       <c r="O8">
-        <v>0.39118576</v>
+        <v>0.3807167200000001</v>
       </c>
       <c r="P8">
-        <v>1.56474304</v>
+        <v>1.52286688</v>
       </c>
       <c r="Q8">
-        <v>4.79474304</v>
+        <v>4.75286688</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09043798172161714</v>
+        <v>0.09082662811682517</v>
       </c>
       <c r="T8">
-        <v>0.8700773483860047</v>
+        <v>0.877652790015764</v>
       </c>
       <c r="U8">
         <v>0.0543</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>7.227660479534578</v>
+        <v>6.195137553886781</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0875095641486474</v>
+        <v>0.0874650254789747</v>
       </c>
       <c r="C9">
-        <v>88.59296513763952</v>
+        <v>87.72701211400314</v>
       </c>
       <c r="D9">
-        <v>91.72096513763952</v>
+        <v>91.81901211400314</v>
       </c>
       <c r="E9">
-        <v>-7.951999999999998</v>
+        <v>-6.987999999999999</v>
       </c>
       <c r="F9">
-        <v>6.748000000000001</v>
+        <v>7.712000000000001</v>
       </c>
       <c r="G9">
         <v>3.62</v>
@@ -2156,45 +2156,45 @@
         <v>2.27</v>
       </c>
       <c r="M9">
-        <v>0.3664164000000001</v>
+        <v>0.4264736000000001</v>
       </c>
       <c r="N9">
-        <v>1.9035836</v>
+        <v>1.8435264</v>
       </c>
       <c r="O9">
-        <v>0.38071672</v>
+        <v>0.36870528</v>
       </c>
       <c r="P9">
-        <v>1.52286688</v>
+        <v>1.47482112</v>
       </c>
       <c r="Q9">
-        <v>4.75286688</v>
+        <v>4.70482112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09082662811682517</v>
+        <v>0.09122372334671161</v>
       </c>
       <c r="T9">
-        <v>0.877652790015764</v>
+        <v>0.8853929151592137</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.195137553886779</v>
+        <v>5.322721031266648</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0874650254789747</v>
+        <v>0.08736448680930198</v>
       </c>
       <c r="C10">
-        <v>87.72701211400314</v>
+        <v>86.98510943884102</v>
       </c>
       <c r="D10">
-        <v>91.81901211400314</v>
+        <v>92.04110943884102</v>
       </c>
       <c r="E10">
-        <v>-6.987999999999999</v>
+        <v>-6.023999999999999</v>
       </c>
       <c r="F10">
-        <v>7.712000000000001</v>
+        <v>8.676</v>
       </c>
       <c r="G10">
         <v>3.62</v>
@@ -2238,28 +2238,28 @@
         <v>2.27</v>
       </c>
       <c r="M10">
-        <v>0.4264736000000001</v>
+        <v>0.4797828</v>
       </c>
       <c r="N10">
-        <v>1.8435264</v>
+        <v>1.7902172</v>
       </c>
       <c r="O10">
-        <v>0.36870528</v>
+        <v>0.35804344</v>
       </c>
       <c r="P10">
-        <v>1.47482112</v>
+        <v>1.43217376</v>
       </c>
       <c r="Q10">
-        <v>4.70482112</v>
+        <v>4.66217376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09122372334671161</v>
+        <v>0.09162954594428788</v>
       </c>
       <c r="T10">
-        <v>0.8853929151592137</v>
+        <v>0.8933031529431787</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.322721031266648</v>
+        <v>4.731307583348132</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08736448680930198</v>
+        <v>0.08746394813962927</v>
       </c>
       <c r="C11">
-        <v>86.98510943884102</v>
+        <v>85.80138635453545</v>
       </c>
       <c r="D11">
-        <v>92.04110943884102</v>
+        <v>91.82138635453545</v>
       </c>
       <c r="E11">
-        <v>-6.023999999999999</v>
+        <v>-5.059999999999999</v>
       </c>
       <c r="F11">
-        <v>8.676</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G11">
         <v>3.62</v>
@@ -2320,45 +2320,45 @@
         <v>2.27</v>
       </c>
       <c r="M11">
-        <v>0.4797828</v>
+        <v>0.557192</v>
       </c>
       <c r="N11">
-        <v>1.7902172</v>
+        <v>1.712808</v>
       </c>
       <c r="O11">
-        <v>0.35804344</v>
+        <v>0.3425616</v>
       </c>
       <c r="P11">
-        <v>1.43217376</v>
+        <v>1.3702464</v>
       </c>
       <c r="Q11">
-        <v>4.66217376</v>
+        <v>4.6002464</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09162954594428788</v>
+        <v>0.09204438682181029</v>
       </c>
       <c r="T11">
-        <v>0.8933031529431787</v>
+        <v>0.9013891737890096</v>
       </c>
       <c r="U11">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.731307583348132</v>
+        <v>4.073999626699593</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08746394813962927</v>
+        <v>0.08793780946995655</v>
       </c>
       <c r="C12">
-        <v>85.80138635453545</v>
+        <v>83.80480766006207</v>
       </c>
       <c r="D12">
-        <v>91.82138635453545</v>
+        <v>90.78880766006206</v>
       </c>
       <c r="E12">
-        <v>-5.059999999999999</v>
+        <v>-4.095999999999998</v>
       </c>
       <c r="F12">
-        <v>9.640000000000001</v>
+        <v>10.604</v>
       </c>
       <c r="G12">
         <v>3.62</v>
@@ -2402,45 +2402,45 @@
         <v>2.27</v>
       </c>
       <c r="M12">
-        <v>0.557192</v>
+        <v>0.6797164000000001</v>
       </c>
       <c r="N12">
-        <v>1.712808</v>
+        <v>1.5902836</v>
       </c>
       <c r="O12">
-        <v>0.3425616</v>
+        <v>0.31805672</v>
       </c>
       <c r="P12">
-        <v>1.3702464</v>
+        <v>1.27222688</v>
       </c>
       <c r="Q12">
-        <v>4.6002464</v>
+        <v>4.50222688</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09204438682181029</v>
+        <v>0.09246854996624332</v>
       </c>
       <c r="T12">
-        <v>0.9013891737890098</v>
+        <v>0.9096569029684549</v>
       </c>
       <c r="U12">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04624</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.073999626699593</v>
+        <v>3.339628115490519</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08793780946995655</v>
+        <v>0.08790767080028383</v>
       </c>
       <c r="C13">
-        <v>83.80480766006207</v>
+        <v>82.90578997402156</v>
       </c>
       <c r="D13">
-        <v>90.78880766006206</v>
+        <v>90.85378997402155</v>
       </c>
       <c r="E13">
-        <v>-4.095999999999998</v>
+        <v>-3.132</v>
       </c>
       <c r="F13">
-        <v>10.604</v>
+        <v>11.568</v>
       </c>
       <c r="G13">
         <v>3.62</v>
@@ -2484,28 +2484,28 @@
         <v>2.27</v>
       </c>
       <c r="M13">
-        <v>0.6797164000000001</v>
+        <v>0.7415088000000001</v>
       </c>
       <c r="N13">
-        <v>1.5902836</v>
+        <v>1.5284912</v>
       </c>
       <c r="O13">
-        <v>0.31805672</v>
+        <v>0.30569824</v>
       </c>
       <c r="P13">
-        <v>1.27222688</v>
+        <v>1.22279296</v>
       </c>
       <c r="Q13">
-        <v>4.50222688</v>
+        <v>4.45279296</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09246854996624332</v>
+        <v>0.09290235318214073</v>
       </c>
       <c r="T13">
-        <v>0.9096569029684549</v>
+        <v>0.9181125350837966</v>
       </c>
       <c r="U13">
         <v>0.0641</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>3.339628115490519</v>
+        <v>3.061325772532976</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08790767080028383</v>
+        <v>0.08868873213061113</v>
       </c>
       <c r="C14">
-        <v>82.90578997402156</v>
+        <v>80.2872206142587</v>
       </c>
       <c r="D14">
-        <v>90.85378997402155</v>
+        <v>89.19922061425869</v>
       </c>
       <c r="E14">
-        <v>-3.132</v>
+        <v>-2.167999999999997</v>
       </c>
       <c r="F14">
-        <v>11.568</v>
+        <v>12.532</v>
       </c>
       <c r="G14">
         <v>3.62</v>
@@ -2566,45 +2566,45 @@
         <v>2.27</v>
       </c>
       <c r="M14">
-        <v>0.7415088000000001</v>
+        <v>0.9010508000000002</v>
       </c>
       <c r="N14">
-        <v>1.5284912</v>
+        <v>1.3689492</v>
       </c>
       <c r="O14">
-        <v>0.30569824</v>
+        <v>0.27378984</v>
       </c>
       <c r="P14">
-        <v>1.22279296</v>
+        <v>1.09515936</v>
       </c>
       <c r="Q14">
-        <v>4.45279296</v>
+        <v>4.32515936</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09290235318214073</v>
+        <v>0.09334612888575991</v>
       </c>
       <c r="T14">
-        <v>0.9181125350837966</v>
+        <v>0.9267625495466173</v>
       </c>
       <c r="U14">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.061325772532976</v>
+        <v>2.519280821902605</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08868873213061113</v>
+        <v>0.08915779346093841</v>
       </c>
       <c r="C15">
-        <v>80.2872206142587</v>
+        <v>78.35822904652187</v>
       </c>
       <c r="D15">
-        <v>89.19922061425869</v>
+        <v>88.23422904652186</v>
       </c>
       <c r="E15">
-        <v>-2.167999999999997</v>
+        <v>-1.203999999999997</v>
       </c>
       <c r="F15">
-        <v>12.532</v>
+        <v>13.496</v>
       </c>
       <c r="G15">
         <v>3.62</v>
@@ -2648,45 +2648,45 @@
         <v>2.27</v>
       </c>
       <c r="M15">
-        <v>0.9010508000000002</v>
+        <v>1.0229968</v>
       </c>
       <c r="N15">
-        <v>1.3689492</v>
+        <v>1.2470032</v>
       </c>
       <c r="O15">
-        <v>0.27378984</v>
+        <v>0.24940064</v>
       </c>
       <c r="P15">
-        <v>1.09515936</v>
+        <v>0.9976025599999998</v>
       </c>
       <c r="Q15">
-        <v>4.32515936</v>
+        <v>4.227602559999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09334612888575991</v>
+        <v>0.09380022495457954</v>
       </c>
       <c r="T15">
-        <v>0.9267625495466173</v>
+        <v>0.9356137271364805</v>
       </c>
       <c r="U15">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.519280821902605</v>
+        <v>2.218970772929103</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08915779346093841</v>
+        <v>0.08922125479126569</v>
       </c>
       <c r="C16">
-        <v>78.35822904652187</v>
+        <v>77.26527235048412</v>
       </c>
       <c r="D16">
-        <v>88.23422904652186</v>
+        <v>88.10527235048413</v>
       </c>
       <c r="E16">
-        <v>-1.203999999999997</v>
+        <v>-0.2399999999999967</v>
       </c>
       <c r="F16">
-        <v>13.496</v>
+        <v>14.46</v>
       </c>
       <c r="G16">
         <v>3.62</v>
@@ -2730,28 +2730,28 @@
         <v>2.27</v>
       </c>
       <c r="M16">
-        <v>1.0229968</v>
+        <v>1.096068</v>
       </c>
       <c r="N16">
-        <v>1.2470032</v>
+        <v>1.173932</v>
       </c>
       <c r="O16">
-        <v>0.24940064</v>
+        <v>0.2347864</v>
       </c>
       <c r="P16">
-        <v>0.9976025599999998</v>
+        <v>0.9391455999999998</v>
       </c>
       <c r="Q16">
-        <v>4.227602559999999</v>
+        <v>4.1691456</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09380022495457954</v>
+        <v>0.09426500563678317</v>
       </c>
       <c r="T16">
-        <v>0.9356137271364805</v>
+        <v>0.944673167728458</v>
       </c>
       <c r="U16">
         <v>0.07580000000000001</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.218970772929103</v>
+        <v>2.071039388067163</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08922125479126569</v>
+        <v>0.09110231612159299</v>
       </c>
       <c r="C17">
-        <v>77.26527235048414</v>
+        <v>72.64292913528024</v>
       </c>
       <c r="D17">
-        <v>88.10527235048413</v>
+        <v>84.44692913528024</v>
       </c>
       <c r="E17">
-        <v>-0.2399999999999984</v>
+        <v>0.724000000000002</v>
       </c>
       <c r="F17">
-        <v>14.46</v>
+        <v>15.424</v>
       </c>
       <c r="G17">
         <v>3.62</v>
@@ -2812,45 +2812,45 @@
         <v>2.27</v>
       </c>
       <c r="M17">
-        <v>1.096068</v>
+        <v>1.38816</v>
       </c>
       <c r="N17">
-        <v>1.173932</v>
+        <v>0.88184</v>
       </c>
       <c r="O17">
-        <v>0.2347864</v>
+        <v>0.176368</v>
       </c>
       <c r="P17">
-        <v>0.9391455999999998</v>
+        <v>0.705472</v>
       </c>
       <c r="Q17">
-        <v>4.1691456</v>
+        <v>3.935472</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09426500563678317</v>
+        <v>0.09474085252570594</v>
       </c>
       <c r="T17">
-        <v>0.944673167728458</v>
+        <v>0.9539483092869111</v>
       </c>
       <c r="U17">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.071039388067163</v>
+        <v>1.635258183494698</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09110231612159299</v>
+        <v>0.09127937745192027</v>
       </c>
       <c r="C18">
-        <v>72.64292913528024</v>
+        <v>71.35015846047158</v>
       </c>
       <c r="D18">
-        <v>84.44692913528024</v>
+        <v>84.11815846047158</v>
       </c>
       <c r="E18">
-        <v>0.724000000000002</v>
+        <v>1.688000000000002</v>
       </c>
       <c r="F18">
-        <v>15.424</v>
+        <v>16.388</v>
       </c>
       <c r="G18">
         <v>3.62</v>
@@ -2894,28 +2894,28 @@
         <v>2.27</v>
       </c>
       <c r="M18">
-        <v>1.38816</v>
+        <v>1.47492</v>
       </c>
       <c r="N18">
-        <v>0.88184</v>
+        <v>0.79508</v>
       </c>
       <c r="O18">
-        <v>0.176368</v>
+        <v>0.159016</v>
       </c>
       <c r="P18">
-        <v>0.705472</v>
+        <v>0.636064</v>
       </c>
       <c r="Q18">
-        <v>3.935472</v>
+        <v>3.866064</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09474085252570594</v>
+        <v>0.09522816560472322</v>
       </c>
       <c r="T18">
-        <v>0.9539483092869111</v>
+        <v>0.963446948232315</v>
       </c>
       <c r="U18">
         <v>0.09</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>1.635258183494698</v>
+        <v>1.539066525642069</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09127937745192027</v>
+        <v>0.1003773172710556</v>
       </c>
       <c r="C19">
-        <v>71.35015846047158</v>
+        <v>56.36381398412031</v>
       </c>
       <c r="D19">
-        <v>84.11815846047158</v>
+        <v>70.09581398412031</v>
       </c>
       <c r="E19">
-        <v>1.688000000000002</v>
+        <v>2.652000000000005</v>
       </c>
       <c r="F19">
-        <v>16.388</v>
+        <v>17.352</v>
       </c>
       <c r="G19">
         <v>3.62</v>
@@ -2976,45 +2976,45 @@
         <v>2.27</v>
       </c>
       <c r="M19">
-        <v>1.47492</v>
+        <v>2.547273600000001</v>
       </c>
       <c r="N19">
-        <v>0.79508</v>
+        <v>-0.2772736000000009</v>
       </c>
       <c r="O19">
-        <v>0.159016</v>
+        <v>-0.05545472000000018</v>
       </c>
       <c r="P19">
-        <v>0.636064</v>
+        <v>-0.2218188800000007</v>
       </c>
       <c r="Q19">
-        <v>3.866064</v>
+        <v>3.008181119999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09522816560472322</v>
+        <v>0.09593031809697597</v>
       </c>
       <c r="T19">
-        <v>0.963446948232315</v>
+        <v>0.9771332072220679</v>
       </c>
       <c r="U19">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V19">
-        <v>0.2</v>
+        <v>0.1782297747678144</v>
       </c>
       <c r="W19">
-        <v>0.07199999999999999</v>
+        <v>0.1206358690640849</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y19">
-        <v>1.539066525642069</v>
+        <v>0.8911488738390722</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1003773172710556</v>
+        <v>0.1013873172710556</v>
       </c>
       <c r="C20">
-        <v>56.3638139841203</v>
+        <v>54.12620022473085</v>
       </c>
       <c r="D20">
-        <v>70.0958139841203</v>
+        <v>68.82220022473085</v>
       </c>
       <c r="E20">
-        <v>2.652000000000001</v>
+        <v>3.616000000000003</v>
       </c>
       <c r="F20">
-        <v>17.352</v>
+        <v>18.316</v>
       </c>
       <c r="G20">
         <v>3.62</v>
@@ -3058,37 +3058,37 @@
         <v>2.27</v>
       </c>
       <c r="M20">
-        <v>2.5472736</v>
+        <v>2.688788800000001</v>
       </c>
       <c r="N20">
-        <v>-0.2772736000000005</v>
+        <v>-0.4187888000000006</v>
       </c>
       <c r="O20">
-        <v>-0.0554547200000001</v>
+        <v>-0.08375776000000013</v>
       </c>
       <c r="P20">
-        <v>-0.2218188800000004</v>
+        <v>-0.3350310400000005</v>
       </c>
       <c r="Q20">
-        <v>3.00818112</v>
+        <v>2.894968959999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09593031809697597</v>
+        <v>0.09654921091298803</v>
       </c>
       <c r="T20">
-        <v>0.9771332072220679</v>
+        <v>0.9891965801507354</v>
       </c>
       <c r="U20">
         <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.1782297747678145</v>
+        <v>0.1688492603063506</v>
       </c>
       <c r="W20">
-        <v>0.1206358690640848</v>
+        <v>0.1220129285870278</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.8911488738390724</v>
+        <v>0.8442463015317527</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1013873172710556</v>
+        <v>0.1023973172710556</v>
       </c>
       <c r="C21">
-        <v>54.12620022473085</v>
+        <v>51.9340426798409</v>
       </c>
       <c r="D21">
-        <v>68.82220022473085</v>
+        <v>67.5940426798409</v>
       </c>
       <c r="E21">
-        <v>3.616000000000003</v>
+        <v>4.580000000000002</v>
       </c>
       <c r="F21">
-        <v>18.316</v>
+        <v>19.28</v>
       </c>
       <c r="G21">
         <v>3.62</v>
@@ -3140,37 +3140,37 @@
         <v>2.27</v>
       </c>
       <c r="M21">
-        <v>2.688788800000001</v>
+        <v>2.830304</v>
       </c>
       <c r="N21">
-        <v>-0.4187888000000006</v>
+        <v>-0.5603040000000004</v>
       </c>
       <c r="O21">
-        <v>-0.08375776000000013</v>
+        <v>-0.1120608000000001</v>
       </c>
       <c r="P21">
-        <v>-0.3350310400000005</v>
+        <v>-0.4482432000000003</v>
       </c>
       <c r="Q21">
-        <v>2.894968959999999</v>
+        <v>2.7817568</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09654921091298803</v>
+        <v>0.09718357604940038</v>
       </c>
       <c r="T21">
-        <v>0.9891965801507354</v>
+        <v>1.00156153740262</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.1688492603063506</v>
+        <v>0.160406797291033</v>
       </c>
       <c r="W21">
-        <v>0.1220129285870278</v>
+        <v>0.1232522821576764</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.8442463015317527</v>
+        <v>0.8020339864551651</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1023973172710556</v>
+        <v>0.1151137196407226</v>
       </c>
       <c r="C22">
-        <v>51.9340426798409</v>
+        <v>38.569134909133</v>
       </c>
       <c r="D22">
-        <v>67.5940426798409</v>
+        <v>55.19313490913301</v>
       </c>
       <c r="E22">
-        <v>4.580000000000002</v>
+        <v>5.544000000000004</v>
       </c>
       <c r="F22">
-        <v>19.28</v>
+        <v>20.244</v>
       </c>
       <c r="G22">
         <v>3.62</v>
@@ -3222,45 +3222,45 @@
         <v>2.27</v>
       </c>
       <c r="M22">
-        <v>2.830304</v>
+        <v>4.064995200000001</v>
       </c>
       <c r="N22">
-        <v>-0.5603040000000004</v>
+        <v>-1.794995200000001</v>
       </c>
       <c r="O22">
-        <v>-0.1120608000000001</v>
+        <v>-0.3589990400000003</v>
       </c>
       <c r="P22">
-        <v>-0.4482432000000003</v>
+        <v>-1.435996160000001</v>
       </c>
       <c r="Q22">
-        <v>2.7817568</v>
+        <v>1.794003839999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09718357604940038</v>
+        <v>0.09829780153061693</v>
       </c>
       <c r="T22">
-        <v>1.00156153740262</v>
+        <v>1.023279865938328</v>
       </c>
       <c r="U22">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.160406797291033</v>
+        <v>0.111685248730429</v>
       </c>
       <c r="W22">
-        <v>0.1232522821576764</v>
+        <v>0.1783736020549299</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y22">
-        <v>0.8020339864551651</v>
+        <v>0.5584262436521449</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1151137196407226</v>
+        <v>0.1166637196407226</v>
       </c>
       <c r="C23">
-        <v>38.56913490913301</v>
+        <v>36.39789713580006</v>
       </c>
       <c r="D23">
-        <v>55.19313490913301</v>
+        <v>53.98589713580007</v>
       </c>
       <c r="E23">
-        <v>5.544</v>
+        <v>6.508000000000003</v>
       </c>
       <c r="F23">
-        <v>20.244</v>
+        <v>21.208</v>
       </c>
       <c r="G23">
         <v>3.62</v>
@@ -3304,37 +3304,37 @@
         <v>2.27</v>
       </c>
       <c r="M23">
-        <v>4.0649952</v>
+        <v>4.2585664</v>
       </c>
       <c r="N23">
-        <v>-1.7949952</v>
+        <v>-1.9885664</v>
       </c>
       <c r="O23">
-        <v>-0.35899904</v>
+        <v>-0.3977132800000001</v>
       </c>
       <c r="P23">
-        <v>-1.43599616</v>
+        <v>-1.59085312</v>
       </c>
       <c r="Q23">
-        <v>1.79400384</v>
+        <v>1.63914688</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09829780153061693</v>
+        <v>0.09897085026818894</v>
       </c>
       <c r="T23">
-        <v>1.023279865938328</v>
+        <v>1.036398838578563</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.111685248730429</v>
+        <v>0.1066086465154095</v>
       </c>
       <c r="W23">
-        <v>0.1783736020549299</v>
+        <v>0.1793929837797058</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.558426243652145</v>
+        <v>0.5330432325770476</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1166637196407226</v>
+        <v>0.1182137196407227</v>
       </c>
       <c r="C24">
-        <v>36.39789713580006</v>
+        <v>34.27834068909831</v>
       </c>
       <c r="D24">
-        <v>53.98589713580007</v>
+        <v>52.83034068909831</v>
       </c>
       <c r="E24">
-        <v>6.508000000000003</v>
+        <v>7.472000000000001</v>
       </c>
       <c r="F24">
-        <v>21.208</v>
+        <v>22.172</v>
       </c>
       <c r="G24">
         <v>3.62</v>
@@ -3386,37 +3386,37 @@
         <v>2.27</v>
       </c>
       <c r="M24">
-        <v>4.2585664</v>
+        <v>4.4521376</v>
       </c>
       <c r="N24">
-        <v>-1.9885664</v>
+        <v>-2.1821376</v>
       </c>
       <c r="O24">
-        <v>-0.3977132800000001</v>
+        <v>-0.4364275200000001</v>
       </c>
       <c r="P24">
-        <v>-1.59085312</v>
+        <v>-1.74571008</v>
       </c>
       <c r="Q24">
-        <v>1.63914688</v>
+        <v>1.48428992</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09897085026818894</v>
+        <v>0.09966138079115244</v>
       </c>
       <c r="T24">
-        <v>1.036398838578563</v>
+        <v>1.049858563754908</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1066086465154095</v>
+        <v>0.1019734879712613</v>
       </c>
       <c r="W24">
-        <v>0.1793929837797058</v>
+        <v>0.1803237236153707</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5330432325770476</v>
+        <v>0.5098674398563063</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1182137196407227</v>
+        <v>0.1283115674225332</v>
       </c>
       <c r="C25">
-        <v>34.27834068909831</v>
+        <v>26.84891098991629</v>
       </c>
       <c r="D25">
-        <v>52.83034068909831</v>
+        <v>46.3649109899163</v>
       </c>
       <c r="E25">
-        <v>7.472000000000001</v>
+        <v>8.436000000000003</v>
       </c>
       <c r="F25">
-        <v>22.172</v>
+        <v>23.136</v>
       </c>
       <c r="G25">
         <v>3.62</v>
@@ -3468,45 +3468,45 @@
         <v>2.27</v>
       </c>
       <c r="M25">
-        <v>4.4521376</v>
+        <v>5.455468800000001</v>
       </c>
       <c r="N25">
-        <v>-2.1821376</v>
+        <v>-3.185468800000001</v>
       </c>
       <c r="O25">
-        <v>-0.4364275200000001</v>
+        <v>-0.6370937600000003</v>
       </c>
       <c r="P25">
-        <v>-1.74571008</v>
+        <v>-2.548375040000001</v>
       </c>
       <c r="Q25">
-        <v>1.48428992</v>
+        <v>0.6816249599999993</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09966138079115244</v>
+        <v>0.1005646197249972</v>
       </c>
       <c r="T25">
-        <v>1.049858563754908</v>
+        <v>1.067464371773286</v>
       </c>
       <c r="U25">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.1019734879712613</v>
+        <v>0.08321924597937393</v>
       </c>
       <c r="W25">
-        <v>0.1803237236153707</v>
+        <v>0.2161769017980636</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.5098674398563063</v>
+        <v>0.4160962298968697</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1283115674225331</v>
+        <v>0.1302115674225331</v>
       </c>
       <c r="C26">
-        <v>26.8489109899163</v>
+        <v>24.84129417801801</v>
       </c>
       <c r="D26">
-        <v>46.3649109899163</v>
+        <v>45.32129417801801</v>
       </c>
       <c r="E26">
-        <v>8.436</v>
+        <v>9.400000000000002</v>
       </c>
       <c r="F26">
-        <v>23.136</v>
+        <v>24.1</v>
       </c>
       <c r="G26">
         <v>3.62</v>
@@ -3550,37 +3550,37 @@
         <v>2.27</v>
       </c>
       <c r="M26">
-        <v>5.4554688</v>
+        <v>5.68278</v>
       </c>
       <c r="N26">
-        <v>-3.1854688</v>
+        <v>-3.41278</v>
       </c>
       <c r="O26">
-        <v>-0.6370937600000001</v>
+        <v>-0.6825560000000001</v>
       </c>
       <c r="P26">
-        <v>-2.54837504</v>
+        <v>-2.730224</v>
       </c>
       <c r="Q26">
-        <v>0.6816249599999997</v>
+        <v>0.4997759999999998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1005646197249972</v>
+        <v>0.1012948146546638</v>
       </c>
       <c r="T26">
-        <v>1.067464371773286</v>
+        <v>1.081697230063596</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.08321924597937395</v>
+        <v>0.07989047614019899</v>
       </c>
       <c r="W26">
-        <v>0.2161769017980636</v>
+        <v>0.2169618257261411</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.4160962298968697</v>
+        <v>0.399452380700995</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1302115674225331</v>
+        <v>0.1321115674225332</v>
       </c>
       <c r="C27">
-        <v>24.84129417801801</v>
+        <v>22.87962420735596</v>
       </c>
       <c r="D27">
-        <v>45.32129417801801</v>
+        <v>44.32362420735596</v>
       </c>
       <c r="E27">
-        <v>9.400000000000002</v>
+        <v>10.364</v>
       </c>
       <c r="F27">
-        <v>24.1</v>
+        <v>25.064</v>
       </c>
       <c r="G27">
         <v>3.62</v>
@@ -3632,37 +3632,37 @@
         <v>2.27</v>
       </c>
       <c r="M27">
-        <v>5.68278</v>
+        <v>5.910091200000001</v>
       </c>
       <c r="N27">
-        <v>-3.41278</v>
+        <v>-3.640091200000001</v>
       </c>
       <c r="O27">
-        <v>-0.6825560000000001</v>
+        <v>-0.7280182400000003</v>
       </c>
       <c r="P27">
-        <v>-2.730224</v>
+        <v>-2.912072960000001</v>
       </c>
       <c r="Q27">
-        <v>0.4997759999999998</v>
+        <v>0.3179270399999994</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1012948146546638</v>
+        <v>0.1020447445824296</v>
       </c>
       <c r="T27">
-        <v>1.081697230063596</v>
+        <v>1.096314760199591</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.07989047614019899</v>
+        <v>0.0768177655194221</v>
       </c>
       <c r="W27">
-        <v>0.2169618257261411</v>
+        <v>0.2176863708905203</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.399452380700995</v>
+        <v>0.3840888275971105</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1321115674225332</v>
+        <v>0.1340115674225331</v>
       </c>
       <c r="C28">
-        <v>22.87962420735596</v>
+        <v>20.96093211362423</v>
       </c>
       <c r="D28">
-        <v>44.32362420735596</v>
+        <v>43.36893211362423</v>
       </c>
       <c r="E28">
-        <v>10.364</v>
+        <v>11.328</v>
       </c>
       <c r="F28">
-        <v>25.064</v>
+        <v>26.028</v>
       </c>
       <c r="G28">
         <v>3.62</v>
@@ -3714,37 +3714,37 @@
         <v>2.27</v>
       </c>
       <c r="M28">
-        <v>5.910091200000001</v>
+        <v>6.137402400000001</v>
       </c>
       <c r="N28">
-        <v>-3.640091200000001</v>
+        <v>-3.867402400000001</v>
       </c>
       <c r="O28">
-        <v>-0.7280182400000003</v>
+        <v>-0.7734804800000002</v>
       </c>
       <c r="P28">
-        <v>-2.912072960000001</v>
+        <v>-3.093921920000001</v>
       </c>
       <c r="Q28">
-        <v>0.3179270399999994</v>
+        <v>0.1360780799999994</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1020447445824296</v>
+        <v>0.1028152205356135</v>
       </c>
       <c r="T28">
-        <v>1.096314760199591</v>
+        <v>1.111332770613284</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.0768177655194221</v>
+        <v>0.07397266309277682</v>
       </c>
       <c r="W28">
-        <v>0.2176863708905203</v>
+        <v>0.2183572460427232</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3840888275971105</v>
+        <v>0.3698633154638842</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1340115674225331</v>
+        <v>0.1359115674225332</v>
       </c>
       <c r="C29">
-        <v>20.96093211362423</v>
+        <v>19.08249933465026</v>
       </c>
       <c r="D29">
-        <v>43.36893211362423</v>
+        <v>42.45449933465027</v>
       </c>
       <c r="E29">
-        <v>11.328</v>
+        <v>12.29200000000001</v>
       </c>
       <c r="F29">
-        <v>26.028</v>
+        <v>26.992</v>
       </c>
       <c r="G29">
         <v>3.62</v>
@@ -3796,37 +3796,37 @@
         <v>2.27</v>
       </c>
       <c r="M29">
-        <v>6.137402400000001</v>
+        <v>6.364713600000002</v>
       </c>
       <c r="N29">
-        <v>-3.867402400000001</v>
+        <v>-4.094713600000002</v>
       </c>
       <c r="O29">
-        <v>-0.7734804800000002</v>
+        <v>-0.8189427200000005</v>
       </c>
       <c r="P29">
-        <v>-3.093921920000001</v>
+        <v>-3.275770880000002</v>
       </c>
       <c r="Q29">
-        <v>0.1360780799999994</v>
+        <v>-0.04577088000000185</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1028152205356135</v>
+        <v>0.1036070985986082</v>
       </c>
       <c r="T29">
-        <v>1.111332770613284</v>
+        <v>1.126767947982913</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.07397266309277682</v>
+        <v>0.07133078226803478</v>
       </c>
       <c r="W29">
-        <v>0.2183572460427232</v>
+        <v>0.2189802015411974</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3698633154638842</v>
+        <v>0.3566539113401739</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1359115674225332</v>
+        <v>0.1378115674225331</v>
       </c>
       <c r="C30">
-        <v>19.08249933465026</v>
+        <v>17.24183185690353</v>
       </c>
       <c r="D30">
-        <v>42.45449933465027</v>
+        <v>41.57783185690354</v>
       </c>
       <c r="E30">
-        <v>12.29200000000001</v>
+        <v>13.25600000000001</v>
       </c>
       <c r="F30">
-        <v>26.992</v>
+        <v>27.95600000000001</v>
       </c>
       <c r="G30">
         <v>3.62</v>
@@ -3878,37 +3878,37 @@
         <v>2.27</v>
       </c>
       <c r="M30">
-        <v>6.364713600000002</v>
+        <v>6.592024800000002</v>
       </c>
       <c r="N30">
-        <v>-4.094713600000002</v>
+        <v>-4.322024800000001</v>
       </c>
       <c r="O30">
-        <v>-0.8189427200000005</v>
+        <v>-0.8644049600000003</v>
       </c>
       <c r="P30">
-        <v>-3.275770880000002</v>
+        <v>-3.457619840000001</v>
       </c>
       <c r="Q30">
-        <v>-0.04577088000000185</v>
+        <v>-0.2276198400000009</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1036070985986082</v>
+        <v>0.1044212830859125</v>
       </c>
       <c r="T30">
-        <v>1.126767947982913</v>
+        <v>1.142637919081264</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.07133078226803478</v>
+        <v>0.06887110012086119</v>
       </c>
       <c r="W30">
-        <v>0.2189802015411974</v>
+        <v>0.2195601945915009</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3566539113401739</v>
+        <v>0.344355500604306</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1378115674225331</v>
+        <v>0.1397115674225332</v>
       </c>
       <c r="C31">
-        <v>17.24183185690354</v>
+        <v>15.43663750037998</v>
       </c>
       <c r="D31">
-        <v>41.57783185690354</v>
+        <v>40.73663750037998</v>
       </c>
       <c r="E31">
-        <v>13.256</v>
+        <v>14.22</v>
       </c>
       <c r="F31">
-        <v>27.956</v>
+        <v>28.92</v>
       </c>
       <c r="G31">
         <v>3.62</v>
@@ -3960,37 +3960,37 @@
         <v>2.27</v>
       </c>
       <c r="M31">
-        <v>6.5920248</v>
+        <v>6.819336000000001</v>
       </c>
       <c r="N31">
-        <v>-4.322024799999999</v>
+        <v>-4.549336</v>
       </c>
       <c r="O31">
-        <v>-0.8644049599999999</v>
+        <v>-0.9098672000000001</v>
       </c>
       <c r="P31">
-        <v>-3.45761984</v>
+        <v>-3.6394688</v>
       </c>
       <c r="Q31">
-        <v>-0.2276198399999996</v>
+        <v>-0.4094688000000004</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1044212830859125</v>
+        <v>0.1052587299871398</v>
       </c>
       <c r="T31">
-        <v>1.142637919081264</v>
+        <v>1.158961317925282</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.0688711001208612</v>
+        <v>0.06657539678349915</v>
       </c>
       <c r="W31">
-        <v>0.2195601945915009</v>
+        <v>0.2201015214384509</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3443555006043061</v>
+        <v>0.3328769839174958</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1397115674225332</v>
+        <v>0.1416115674225332</v>
       </c>
       <c r="C32">
-        <v>15.43663750037998</v>
+        <v>13.66480590621153</v>
       </c>
       <c r="D32">
-        <v>40.73663750037998</v>
+        <v>39.92880590621153</v>
       </c>
       <c r="E32">
-        <v>14.22</v>
+        <v>15.184</v>
       </c>
       <c r="F32">
-        <v>28.92</v>
+        <v>29.884</v>
       </c>
       <c r="G32">
         <v>3.62</v>
@@ -4042,37 +4042,37 @@
         <v>2.27</v>
       </c>
       <c r="M32">
-        <v>6.819336000000001</v>
+        <v>7.046647200000001</v>
       </c>
       <c r="N32">
-        <v>-4.549336</v>
+        <v>-4.776647200000001</v>
       </c>
       <c r="O32">
-        <v>-0.9098672000000001</v>
+        <v>-0.9553294400000003</v>
       </c>
       <c r="P32">
-        <v>-3.6394688</v>
+        <v>-3.821317760000001</v>
       </c>
       <c r="Q32">
-        <v>-0.4094688000000004</v>
+        <v>-0.5913177600000008</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1052587299871398</v>
+        <v>0.1061204507115911</v>
       </c>
       <c r="T32">
-        <v>1.158961317925282</v>
+        <v>1.175757858764779</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.06657539678349915</v>
+        <v>0.06442780333887015</v>
       </c>
       <c r="W32">
-        <v>0.2201015214384509</v>
+        <v>0.2206079239726944</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3328769839174958</v>
+        <v>0.3221390166943506</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1416115674225332</v>
+        <v>0.1435115674225332</v>
       </c>
       <c r="C33">
-        <v>13.66480590621153</v>
+        <v>11.92439085911951</v>
       </c>
       <c r="D33">
-        <v>39.92880590621153</v>
+        <v>39.15239085911951</v>
       </c>
       <c r="E33">
-        <v>15.184</v>
+        <v>16.148</v>
       </c>
       <c r="F33">
-        <v>29.884</v>
+        <v>30.848</v>
       </c>
       <c r="G33">
         <v>3.62</v>
@@ -4124,37 +4124,37 @@
         <v>2.27</v>
       </c>
       <c r="M33">
-        <v>7.046647200000001</v>
+        <v>7.273958400000001</v>
       </c>
       <c r="N33">
-        <v>-4.776647200000001</v>
+        <v>-5.0039584</v>
       </c>
       <c r="O33">
-        <v>-0.9553294400000003</v>
+        <v>-1.00079168</v>
       </c>
       <c r="P33">
-        <v>-3.821317760000001</v>
+        <v>-4.00316672</v>
       </c>
       <c r="Q33">
-        <v>-0.5913177600000008</v>
+        <v>-0.7731667200000003</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1061204507115911</v>
+        <v>0.1070075161632322</v>
       </c>
       <c r="T33">
-        <v>1.175757858764779</v>
+        <v>1.193048415511319</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.06442780333887015</v>
+        <v>0.06241443448453046</v>
       </c>
       <c r="W33">
-        <v>0.2206079239726944</v>
+        <v>0.2210826763485477</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3221390166943506</v>
+        <v>0.3120721724226523</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1435115674225332</v>
+        <v>0.1454115674225331</v>
       </c>
       <c r="C34">
-        <v>11.92439085911951</v>
+        <v>10.21359463296657</v>
       </c>
       <c r="D34">
-        <v>39.15239085911951</v>
+        <v>38.40559463296658</v>
       </c>
       <c r="E34">
-        <v>16.148</v>
+        <v>17.11200000000001</v>
       </c>
       <c r="F34">
-        <v>30.848</v>
+        <v>31.812</v>
       </c>
       <c r="G34">
         <v>3.62</v>
@@ -4206,37 +4206,37 @@
         <v>2.27</v>
       </c>
       <c r="M34">
-        <v>7.273958400000001</v>
+        <v>7.501269600000001</v>
       </c>
       <c r="N34">
-        <v>-5.0039584</v>
+        <v>-5.231269600000001</v>
       </c>
       <c r="O34">
-        <v>-1.00079168</v>
+        <v>-1.04625392</v>
       </c>
       <c r="P34">
-        <v>-4.00316672</v>
+        <v>-4.185015680000001</v>
       </c>
       <c r="Q34">
-        <v>-0.7731667200000003</v>
+        <v>-0.9550156800000011</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1070075161632322</v>
+        <v>0.1079210611805938</v>
       </c>
       <c r="T34">
-        <v>1.193048415511319</v>
+        <v>1.210855108280145</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06241443448453046</v>
+        <v>0.06052308798499922</v>
       </c>
       <c r="W34">
-        <v>0.2210826763485477</v>
+        <v>0.2215286558531372</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3120721724226523</v>
+        <v>0.3026154399249962</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1454115674225331</v>
+        <v>0.1473115674225332</v>
       </c>
       <c r="C35">
-        <v>10.21359463296657</v>
+        <v>8.530754094342008</v>
       </c>
       <c r="D35">
-        <v>38.40559463296658</v>
+        <v>37.68675409434201</v>
       </c>
       <c r="E35">
-        <v>17.11200000000001</v>
+        <v>18.076</v>
       </c>
       <c r="F35">
-        <v>31.812</v>
+        <v>32.776</v>
       </c>
       <c r="G35">
         <v>3.62</v>
@@ -4288,37 +4288,37 @@
         <v>2.27</v>
       </c>
       <c r="M35">
-        <v>7.501269600000001</v>
+        <v>7.728580800000001</v>
       </c>
       <c r="N35">
-        <v>-5.231269600000001</v>
+        <v>-5.458580800000002</v>
       </c>
       <c r="O35">
-        <v>-1.04625392</v>
+        <v>-1.09171616</v>
       </c>
       <c r="P35">
-        <v>-4.185015680000001</v>
+        <v>-4.366864640000001</v>
       </c>
       <c r="Q35">
-        <v>-0.9550156800000011</v>
+        <v>-1.136864640000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1079210611805938</v>
+        <v>0.1088622893802998</v>
       </c>
       <c r="T35">
-        <v>1.210855108280145</v>
+        <v>1.229201397799541</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.06052308798499922</v>
+        <v>0.05874299716191102</v>
       </c>
       <c r="W35">
-        <v>0.2215286558531372</v>
+        <v>0.2219484012692214</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3026154399249962</v>
+        <v>0.293714985809555</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1473115674225332</v>
+        <v>0.1492115674225331</v>
       </c>
       <c r="C36">
-        <v>8.530754094342008</v>
+        <v>6.874328338075536</v>
       </c>
       <c r="D36">
-        <v>37.68675409434201</v>
+        <v>36.99432833807554</v>
       </c>
       <c r="E36">
-        <v>18.076</v>
+        <v>19.04</v>
       </c>
       <c r="F36">
-        <v>32.776</v>
+        <v>33.74</v>
       </c>
       <c r="G36">
         <v>3.62</v>
@@ -4370,37 +4370,37 @@
         <v>2.27</v>
       </c>
       <c r="M36">
-        <v>7.728580800000001</v>
+        <v>7.955892</v>
       </c>
       <c r="N36">
-        <v>-5.458580800000002</v>
+        <v>-5.685892000000001</v>
       </c>
       <c r="O36">
-        <v>-1.09171616</v>
+        <v>-1.1371784</v>
       </c>
       <c r="P36">
-        <v>-4.366864640000001</v>
+        <v>-4.548713600000001</v>
       </c>
       <c r="Q36">
-        <v>-1.136864640000001</v>
+        <v>-1.318713600000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1088622893802998</v>
+        <v>0.109832478447689</v>
       </c>
       <c r="T36">
-        <v>1.229201397799541</v>
+        <v>1.248112188534919</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05874299716191102</v>
+        <v>0.05706462581442785</v>
       </c>
       <c r="W36">
-        <v>0.2219484012692214</v>
+        <v>0.2223441612329579</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.293714985809555</v>
+        <v>0.2853231290721392</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1492115674225331</v>
+        <v>0.1511115674225331</v>
       </c>
       <c r="C37">
-        <v>6.874328338075536</v>
+        <v>5.242887661209259</v>
       </c>
       <c r="D37">
-        <v>36.99432833807554</v>
+        <v>36.32688766120927</v>
       </c>
       <c r="E37">
-        <v>19.04</v>
+        <v>20.00400000000001</v>
       </c>
       <c r="F37">
-        <v>33.74</v>
+        <v>34.70400000000001</v>
       </c>
       <c r="G37">
         <v>3.62</v>
@@ -4452,37 +4452,37 @@
         <v>2.27</v>
       </c>
       <c r="M37">
-        <v>7.955892</v>
+        <v>8.183203200000003</v>
       </c>
       <c r="N37">
-        <v>-5.685892000000001</v>
+        <v>-5.913203200000003</v>
       </c>
       <c r="O37">
-        <v>-1.1371784</v>
+        <v>-1.182640640000001</v>
       </c>
       <c r="P37">
-        <v>-4.548713600000001</v>
+        <v>-4.730562560000003</v>
       </c>
       <c r="Q37">
-        <v>-1.318713600000001</v>
+        <v>-1.500562560000003</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.109832478447689</v>
+        <v>0.1108329859234342</v>
       </c>
       <c r="T37">
-        <v>1.248112188534919</v>
+        <v>1.267613941480777</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.05706462581442785</v>
+        <v>0.05547949731958261</v>
       </c>
       <c r="W37">
-        <v>0.2223441612329579</v>
+        <v>0.2227179345320424</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2853231290721392</v>
+        <v>0.277397486597913</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1511115674225331</v>
+        <v>0.1530115674225331</v>
       </c>
       <c r="C38">
-        <v>5.242887661209274</v>
+        <v>3.635103709387373</v>
       </c>
       <c r="D38">
-        <v>36.32688766120928</v>
+        <v>35.68310370938737</v>
       </c>
       <c r="E38">
-        <v>20.004</v>
+        <v>20.968</v>
       </c>
       <c r="F38">
-        <v>34.704</v>
+        <v>35.668</v>
       </c>
       <c r="G38">
         <v>3.62</v>
@@ -4534,37 +4534,37 @@
         <v>2.27</v>
       </c>
       <c r="M38">
-        <v>8.183203200000001</v>
+        <v>8.4105144</v>
       </c>
       <c r="N38">
-        <v>-5.913203200000002</v>
+        <v>-6.140514400000001</v>
       </c>
       <c r="O38">
-        <v>-1.18264064</v>
+        <v>-1.22810288</v>
       </c>
       <c r="P38">
-        <v>-4.730562560000001</v>
+        <v>-4.912411520000001</v>
       </c>
       <c r="Q38">
-        <v>-1.500562560000001</v>
+        <v>-1.682411520000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1108329859234342</v>
+        <v>0.1118652555412665</v>
       </c>
       <c r="T38">
-        <v>1.267613941480777</v>
+        <v>1.287734797694758</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05547949731958263</v>
+        <v>0.0539800514460804</v>
       </c>
       <c r="W38">
-        <v>0.2227179345320424</v>
+        <v>0.2230715038690143</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2773974865979131</v>
+        <v>0.2699002572304019</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1530115674225331</v>
+        <v>0.1549115674225331</v>
       </c>
       <c r="C39">
-        <v>3.635103709387373</v>
+        <v>2.049740652752959</v>
       </c>
       <c r="D39">
-        <v>35.68310370938737</v>
+        <v>35.06174065275297</v>
       </c>
       <c r="E39">
-        <v>20.968</v>
+        <v>21.93200000000001</v>
       </c>
       <c r="F39">
-        <v>35.668</v>
+        <v>36.63200000000001</v>
       </c>
       <c r="G39">
         <v>3.62</v>
@@ -4616,37 +4616,37 @@
         <v>2.27</v>
       </c>
       <c r="M39">
-        <v>8.4105144</v>
+        <v>8.637825600000001</v>
       </c>
       <c r="N39">
-        <v>-6.140514400000001</v>
+        <v>-6.367825600000002</v>
       </c>
       <c r="O39">
-        <v>-1.22810288</v>
+        <v>-1.27356512</v>
       </c>
       <c r="P39">
-        <v>-4.912411520000001</v>
+        <v>-5.094260480000001</v>
       </c>
       <c r="Q39">
-        <v>-1.682411520000001</v>
+        <v>-1.864260480000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1118652555412665</v>
+        <v>0.1129308241790288</v>
       </c>
       <c r="T39">
-        <v>1.287734797694758</v>
+        <v>1.308504713786608</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0539800514460804</v>
+        <v>0.0525595237764467</v>
       </c>
       <c r="W39">
-        <v>0.2230715038690143</v>
+        <v>0.2234064642935139</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2699002572304019</v>
+        <v>0.2627976188822334</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1549115674225331</v>
+        <v>0.1568115674225332</v>
       </c>
       <c r="C40">
-        <v>2.049740652752959</v>
+        <v>0.4856472680098065</v>
       </c>
       <c r="D40">
-        <v>35.06174065275297</v>
+        <v>34.46164726800981</v>
       </c>
       <c r="E40">
-        <v>21.93200000000001</v>
+        <v>22.896</v>
       </c>
       <c r="F40">
-        <v>36.63200000000001</v>
+        <v>37.596</v>
       </c>
       <c r="G40">
         <v>3.62</v>
@@ -4698,37 +4698,37 @@
         <v>2.27</v>
       </c>
       <c r="M40">
-        <v>8.637825600000001</v>
+        <v>8.865136800000002</v>
       </c>
       <c r="N40">
-        <v>-6.367825600000002</v>
+        <v>-6.595136800000002</v>
       </c>
       <c r="O40">
-        <v>-1.27356512</v>
+        <v>-1.319027360000001</v>
       </c>
       <c r="P40">
-        <v>-5.094260480000001</v>
+        <v>-5.276109440000002</v>
       </c>
       <c r="Q40">
-        <v>-1.864260480000001</v>
+        <v>-2.046109440000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1129308241790288</v>
+        <v>0.1140313294934391</v>
       </c>
       <c r="T40">
-        <v>1.308504713786608</v>
+        <v>1.32995561073393</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.0525595237764467</v>
+        <v>0.05121184367961473</v>
       </c>
       <c r="W40">
-        <v>0.2234064642935139</v>
+        <v>0.2237242472603468</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2627976188822334</v>
+        <v>0.2560592183980736</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1568115674225332</v>
+        <v>0.1587115674225331</v>
       </c>
       <c r="C41">
-        <v>0.4856472680098065</v>
+        <v>-1.058250180089473</v>
       </c>
       <c r="D41">
-        <v>34.46164726800981</v>
+        <v>33.88174981991053</v>
       </c>
       <c r="E41">
-        <v>22.896</v>
+        <v>23.86</v>
       </c>
       <c r="F41">
-        <v>37.596</v>
+        <v>38.56</v>
       </c>
       <c r="G41">
         <v>3.62</v>
@@ -4780,37 +4780,37 @@
         <v>2.27</v>
       </c>
       <c r="M41">
-        <v>8.865136800000002</v>
+        <v>9.092448000000001</v>
       </c>
       <c r="N41">
-        <v>-6.595136800000002</v>
+        <v>-6.822448000000001</v>
       </c>
       <c r="O41">
-        <v>-1.319027360000001</v>
+        <v>-1.3644896</v>
       </c>
       <c r="P41">
-        <v>-5.276109440000002</v>
+        <v>-5.457958400000001</v>
       </c>
       <c r="Q41">
-        <v>-2.046109440000002</v>
+        <v>-2.227958400000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1140313294934391</v>
+        <v>0.1151685183183298</v>
       </c>
       <c r="T41">
-        <v>1.32995561073393</v>
+        <v>1.352121537579495</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05121184367961473</v>
+        <v>0.04993154758762437</v>
       </c>
       <c r="W41">
-        <v>0.2237242472603468</v>
+        <v>0.2240261410788382</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2560592183980736</v>
+        <v>0.2496577379381217</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1587115674225331</v>
+        <v>0.1606115674225332</v>
       </c>
       <c r="C42">
-        <v>-1.058250180089473</v>
+        <v>-2.582954350435976</v>
       </c>
       <c r="D42">
-        <v>33.88174981991053</v>
+        <v>33.32104564956403</v>
       </c>
       <c r="E42">
-        <v>23.86</v>
+        <v>24.82400000000001</v>
       </c>
       <c r="F42">
-        <v>38.56</v>
+        <v>39.52400000000001</v>
       </c>
       <c r="G42">
         <v>3.62</v>
@@ -4862,37 +4862,37 @@
         <v>2.27</v>
       </c>
       <c r="M42">
-        <v>9.092448000000001</v>
+        <v>9.319759200000002</v>
       </c>
       <c r="N42">
-        <v>-6.822448000000001</v>
+        <v>-7.049759200000002</v>
       </c>
       <c r="O42">
-        <v>-1.3644896</v>
+        <v>-1.409951840000001</v>
       </c>
       <c r="P42">
-        <v>-5.457958400000001</v>
+        <v>-5.639807360000002</v>
       </c>
       <c r="Q42">
-        <v>-2.227958400000001</v>
+        <v>-2.409807360000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1151685183183298</v>
+        <v>0.1163442559169456</v>
       </c>
       <c r="T42">
-        <v>1.352121537579495</v>
+        <v>1.375038851775758</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04993154758762437</v>
+        <v>0.04871370496353596</v>
       </c>
       <c r="W42">
-        <v>0.2240261410788382</v>
+        <v>0.2243133083695982</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2496577379381217</v>
+        <v>0.2435685248176798</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1606115674225332</v>
+        <v>0.1625115674225331</v>
       </c>
       <c r="C43">
-        <v>-2.582954350435976</v>
+        <v>-4.089402610983861</v>
       </c>
       <c r="D43">
-        <v>33.32104564956403</v>
+        <v>32.77859738901615</v>
       </c>
       <c r="E43">
-        <v>24.82400000000001</v>
+        <v>25.78800000000001</v>
       </c>
       <c r="F43">
-        <v>39.52400000000001</v>
+        <v>40.48800000000001</v>
       </c>
       <c r="G43">
         <v>3.62</v>
@@ -4944,37 +4944,37 @@
         <v>2.27</v>
       </c>
       <c r="M43">
-        <v>9.319759200000002</v>
+        <v>9.547070400000003</v>
       </c>
       <c r="N43">
-        <v>-7.049759200000002</v>
+        <v>-7.277070400000003</v>
       </c>
       <c r="O43">
-        <v>-1.409951840000001</v>
+        <v>-1.455414080000001</v>
       </c>
       <c r="P43">
-        <v>-5.639807360000002</v>
+        <v>-5.821656320000002</v>
       </c>
       <c r="Q43">
-        <v>-2.409807360000002</v>
+        <v>-2.591656320000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1163442559169456</v>
+        <v>0.1175605361913757</v>
       </c>
       <c r="T43">
-        <v>1.375038851775758</v>
+        <v>1.398746418185685</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04871370496353596</v>
+        <v>0.04755385484535653</v>
       </c>
       <c r="W43">
-        <v>0.2243133083695982</v>
+        <v>0.2245868010274649</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2435685248176798</v>
+        <v>0.2377692742267826</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1625115674225331</v>
+        <v>0.1644115674225332</v>
       </c>
       <c r="C44">
-        <v>-4.089402610983853</v>
+        <v>-5.578472268121693</v>
       </c>
       <c r="D44">
-        <v>32.77859738901615</v>
+        <v>32.25352773187831</v>
       </c>
       <c r="E44">
-        <v>25.788</v>
+        <v>26.75200000000001</v>
       </c>
       <c r="F44">
-        <v>40.488</v>
+        <v>41.45200000000001</v>
       </c>
       <c r="G44">
         <v>3.62</v>
@@ -5026,37 +5026,37 @@
         <v>2.27</v>
       </c>
       <c r="M44">
-        <v>9.547070400000001</v>
+        <v>9.774381600000002</v>
       </c>
       <c r="N44">
-        <v>-7.277070400000001</v>
+        <v>-7.504381600000002</v>
       </c>
       <c r="O44">
-        <v>-1.45541408</v>
+        <v>-1.500876320000001</v>
       </c>
       <c r="P44">
-        <v>-5.821656320000001</v>
+        <v>-6.003505280000001</v>
       </c>
       <c r="Q44">
-        <v>-2.591656320000001</v>
+        <v>-2.773505280000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1175605361913756</v>
+        <v>0.1188194929666629</v>
       </c>
       <c r="T44">
-        <v>1.398746418185685</v>
+        <v>1.423285829031048</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04755385484535654</v>
+        <v>0.04644795124430173</v>
       </c>
       <c r="W44">
-        <v>0.2245868010274649</v>
+        <v>0.2248475730965937</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2377692742267826</v>
+        <v>0.2322397562215086</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1644115674225332</v>
+        <v>0.1663115674225332</v>
       </c>
       <c r="C45">
-        <v>-5.578472268121693</v>
+        <v>-7.050985301361948</v>
       </c>
       <c r="D45">
-        <v>32.25352773187831</v>
+        <v>31.74501469863806</v>
       </c>
       <c r="E45">
-        <v>26.75200000000001</v>
+        <v>27.716</v>
       </c>
       <c r="F45">
-        <v>41.45200000000001</v>
+        <v>42.416</v>
       </c>
       <c r="G45">
         <v>3.62</v>
@@ -5108,37 +5108,37 @@
         <v>2.27</v>
       </c>
       <c r="M45">
-        <v>9.774381600000002</v>
+        <v>10.0016928</v>
       </c>
       <c r="N45">
-        <v>-7.504381600000002</v>
+        <v>-7.731692800000001</v>
       </c>
       <c r="O45">
-        <v>-1.500876320000001</v>
+        <v>-1.54633856</v>
       </c>
       <c r="P45">
-        <v>-6.003505280000001</v>
+        <v>-6.185354240000001</v>
       </c>
       <c r="Q45">
-        <v>-2.773505280000002</v>
+        <v>-2.955354240000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1188194929666629</v>
+        <v>0.1201234124839248</v>
       </c>
       <c r="T45">
-        <v>1.423285829031048</v>
+        <v>1.448701647406602</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04644795124430173</v>
+        <v>0.04539231598874943</v>
       </c>
       <c r="W45">
-        <v>0.2248475730965937</v>
+        <v>0.2250964918898529</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2322397562215086</v>
+        <v>0.2269615799437471</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1663115674225332</v>
+        <v>0.1682115674225331</v>
       </c>
       <c r="C46">
-        <v>-7.050985301361948</v>
+        <v>-8.507712657096363</v>
       </c>
       <c r="D46">
-        <v>31.74501469863806</v>
+        <v>31.25228734290364</v>
       </c>
       <c r="E46">
-        <v>27.716</v>
+        <v>28.68</v>
       </c>
       <c r="F46">
-        <v>42.416</v>
+        <v>43.38</v>
       </c>
       <c r="G46">
         <v>3.62</v>
@@ -5190,37 +5190,37 @@
         <v>2.27</v>
       </c>
       <c r="M46">
-        <v>10.0016928</v>
+        <v>10.229004</v>
       </c>
       <c r="N46">
-        <v>-7.731692800000001</v>
+        <v>-7.959004000000002</v>
       </c>
       <c r="O46">
-        <v>-1.54633856</v>
+        <v>-1.591800800000001</v>
       </c>
       <c r="P46">
-        <v>-6.185354240000001</v>
+        <v>-6.367203200000001</v>
       </c>
       <c r="Q46">
-        <v>-2.955354240000001</v>
+        <v>-3.137203200000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1201234124839248</v>
+        <v>0.1214747472563598</v>
       </c>
       <c r="T46">
-        <v>1.448701647406602</v>
+        <v>1.475041677359449</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04539231598874943</v>
+        <v>0.0443835978556661</v>
       </c>
       <c r="W46">
-        <v>0.2250964918898529</v>
+        <v>0.2253343476256339</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2269615799437471</v>
+        <v>0.2219179892783304</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1682115674225331</v>
+        <v>0.1701115674225332</v>
       </c>
       <c r="C47">
-        <v>-8.507712657096363</v>
+        <v>-9.949378148592338</v>
       </c>
       <c r="D47">
-        <v>31.25228734290364</v>
+        <v>30.77462185140767</v>
       </c>
       <c r="E47">
-        <v>28.68</v>
+        <v>29.644</v>
       </c>
       <c r="F47">
-        <v>43.38</v>
+        <v>44.344</v>
       </c>
       <c r="G47">
         <v>3.62</v>
@@ -5272,37 +5272,37 @@
         <v>2.27</v>
       </c>
       <c r="M47">
-        <v>10.229004</v>
+        <v>10.4563152</v>
       </c>
       <c r="N47">
-        <v>-7.959004000000002</v>
+        <v>-8.186315200000001</v>
       </c>
       <c r="O47">
-        <v>-1.591800800000001</v>
+        <v>-1.63726304</v>
       </c>
       <c r="P47">
-        <v>-6.367203200000001</v>
+        <v>-6.54905216</v>
       </c>
       <c r="Q47">
-        <v>-3.137203200000001</v>
+        <v>-3.31905216</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1214747472563598</v>
+        <v>0.1228761314648109</v>
       </c>
       <c r="T47">
-        <v>1.475041677359449</v>
+        <v>1.502357263977217</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0443835978556661</v>
+        <v>0.04341873703271684</v>
       </c>
       <c r="W47">
-        <v>0.2253343476256339</v>
+        <v>0.2255618618076854</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2219179892783304</v>
+        <v>0.2170936851635842</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1701115674225332</v>
+        <v>0.1720115674225332</v>
       </c>
       <c r="C48">
-        <v>-9.949378148592338</v>
+        <v>-11.37666200372363</v>
       </c>
       <c r="D48">
-        <v>30.77462185140767</v>
+        <v>30.31133799627638</v>
       </c>
       <c r="E48">
-        <v>29.644</v>
+        <v>30.60800000000001</v>
       </c>
       <c r="F48">
-        <v>44.344</v>
+        <v>45.30800000000001</v>
       </c>
       <c r="G48">
         <v>3.62</v>
@@ -5354,37 +5354,37 @@
         <v>2.27</v>
       </c>
       <c r="M48">
-        <v>10.4563152</v>
+        <v>10.6836264</v>
       </c>
       <c r="N48">
-        <v>-8.186315200000001</v>
+        <v>-8.413626400000002</v>
       </c>
       <c r="O48">
-        <v>-1.63726304</v>
+        <v>-1.682725280000001</v>
       </c>
       <c r="P48">
-        <v>-6.54905216</v>
+        <v>-6.730901120000001</v>
       </c>
       <c r="Q48">
-        <v>-3.31905216</v>
+        <v>-3.500901120000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1228761314648109</v>
+        <v>0.1243303980962224</v>
       </c>
       <c r="T48">
-        <v>1.502357263977217</v>
+        <v>1.530703627448485</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04341873703271684</v>
+        <v>0.04249493411712712</v>
       </c>
       <c r="W48">
-        <v>0.2255618618076854</v>
+        <v>0.2257796945351814</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2170936851635842</v>
+        <v>0.2124746705856355</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1720115674225332</v>
+        <v>0.1739115674225332</v>
       </c>
       <c r="C49">
-        <v>-11.37666200372363</v>
+        <v>-12.79020409700689</v>
       </c>
       <c r="D49">
-        <v>30.31133799627638</v>
+        <v>29.86179590299311</v>
       </c>
       <c r="E49">
-        <v>30.60800000000001</v>
+        <v>31.57200000000001</v>
       </c>
       <c r="F49">
-        <v>45.30800000000001</v>
+        <v>46.27200000000001</v>
       </c>
       <c r="G49">
         <v>3.62</v>
@@ -5436,37 +5436,37 @@
         <v>2.27</v>
       </c>
       <c r="M49">
-        <v>10.6836264</v>
+        <v>10.9109376</v>
       </c>
       <c r="N49">
-        <v>-8.413626400000002</v>
+        <v>-8.640937600000003</v>
       </c>
       <c r="O49">
-        <v>-1.682725280000001</v>
+        <v>-1.728187520000001</v>
       </c>
       <c r="P49">
-        <v>-6.730901120000001</v>
+        <v>-6.912750080000002</v>
       </c>
       <c r="Q49">
-        <v>-3.500901120000001</v>
+        <v>-3.682750080000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1243303980962224</v>
+        <v>0.1258405980596113</v>
       </c>
       <c r="T49">
-        <v>1.530703627448485</v>
+        <v>1.560140235668649</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04249493411712712</v>
+        <v>0.04160962298968696</v>
       </c>
       <c r="W49">
-        <v>0.2257796945351814</v>
+        <v>0.2259884508990318</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2124746705856355</v>
+        <v>0.2080481149484348</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1739115674225332</v>
+        <v>0.1758115674225331</v>
       </c>
       <c r="C50">
-        <v>-12.79020409700689</v>
+        <v>-14.19060689823835</v>
       </c>
       <c r="D50">
-        <v>29.86179590299311</v>
+        <v>29.42539310176165</v>
       </c>
       <c r="E50">
-        <v>31.572</v>
+        <v>32.536</v>
       </c>
       <c r="F50">
-        <v>46.272</v>
+        <v>47.236</v>
       </c>
       <c r="G50">
         <v>3.62</v>
@@ -5518,37 +5518,37 @@
         <v>2.27</v>
       </c>
       <c r="M50">
-        <v>10.9109376</v>
+        <v>11.1382488</v>
       </c>
       <c r="N50">
-        <v>-8.640937600000001</v>
+        <v>-8.868248800000002</v>
       </c>
       <c r="O50">
-        <v>-1.72818752</v>
+        <v>-1.773649760000001</v>
       </c>
       <c r="P50">
-        <v>-6.91275008</v>
+        <v>-7.094599040000001</v>
       </c>
       <c r="Q50">
-        <v>-3.68275008</v>
+        <v>-3.864599040000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1258405980596113</v>
+        <v>0.1274100215509762</v>
       </c>
       <c r="T50">
-        <v>1.560140235668648</v>
+        <v>1.590731220681759</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04160962298968698</v>
+        <v>0.0407604470103056</v>
       </c>
       <c r="W50">
-        <v>0.2259884508990318</v>
+        <v>0.22618868659497</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2080481149484348</v>
+        <v>0.2038022350515279</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1758115674225331</v>
+        <v>0.1777115674225331</v>
       </c>
       <c r="C51">
-        <v>-14.19060689823835</v>
+        <v>-15.57843816630497</v>
       </c>
       <c r="D51">
-        <v>29.42539310176165</v>
+        <v>29.00156183369504</v>
       </c>
       <c r="E51">
-        <v>32.536</v>
+        <v>33.5</v>
       </c>
       <c r="F51">
-        <v>47.236</v>
+        <v>48.2</v>
       </c>
       <c r="G51">
         <v>3.62</v>
@@ -5600,37 +5600,37 @@
         <v>2.27</v>
       </c>
       <c r="M51">
-        <v>11.1382488</v>
+        <v>11.36556</v>
       </c>
       <c r="N51">
-        <v>-8.868248800000002</v>
+        <v>-9.095560000000001</v>
       </c>
       <c r="O51">
-        <v>-1.773649760000001</v>
+        <v>-1.819112</v>
       </c>
       <c r="P51">
-        <v>-7.094599040000001</v>
+        <v>-7.276448</v>
       </c>
       <c r="Q51">
-        <v>-3.864599040000001</v>
+        <v>-4.046448</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1274100215509762</v>
+        <v>0.1290422219819957</v>
       </c>
       <c r="T51">
-        <v>1.590731220681759</v>
+        <v>1.622545845095394</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0407604470103056</v>
+        <v>0.0399452380700995</v>
       </c>
       <c r="W51">
-        <v>0.22618868659497</v>
+        <v>0.2263809128630705</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2038022350515279</v>
+        <v>0.1997261903504974</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1777115674225331</v>
+        <v>0.1796115674225331</v>
       </c>
       <c r="C52">
-        <v>-15.57843816630497</v>
+        <v>-16.95423341349779</v>
       </c>
       <c r="D52">
-        <v>29.00156183369504</v>
+        <v>28.58976658650221</v>
       </c>
       <c r="E52">
-        <v>33.5</v>
+        <v>34.464</v>
       </c>
       <c r="F52">
-        <v>48.2</v>
+        <v>49.164</v>
       </c>
       <c r="G52">
         <v>3.62</v>
@@ -5682,37 +5682,37 @@
         <v>2.27</v>
       </c>
       <c r="M52">
-        <v>11.36556</v>
+        <v>11.5928712</v>
       </c>
       <c r="N52">
-        <v>-9.095560000000001</v>
+        <v>-9.322871200000002</v>
       </c>
       <c r="O52">
-        <v>-1.819112</v>
+        <v>-1.86457424</v>
       </c>
       <c r="P52">
-        <v>-7.276448</v>
+        <v>-7.458296960000001</v>
       </c>
       <c r="Q52">
-        <v>-4.046448</v>
+        <v>-4.228296960000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1290422219819957</v>
+        <v>0.1307410428387712</v>
       </c>
       <c r="T52">
-        <v>1.622545845095394</v>
+        <v>1.655659025607546</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0399452380700995</v>
+        <v>0.03916199810794068</v>
       </c>
       <c r="W52">
-        <v>0.2263809128630705</v>
+        <v>0.2265656008461476</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1997261903504974</v>
+        <v>0.1958099905397034</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1796115674225331</v>
+        <v>0.1815115674225331</v>
       </c>
       <c r="C53">
-        <v>-16.95423341349779</v>
+        <v>-18.31849816281889</v>
       </c>
       <c r="D53">
-        <v>28.58976658650221</v>
+        <v>28.18950183718112</v>
       </c>
       <c r="E53">
-        <v>34.464</v>
+        <v>35.42800000000001</v>
       </c>
       <c r="F53">
-        <v>49.164</v>
+        <v>50.12800000000001</v>
       </c>
       <c r="G53">
         <v>3.62</v>
@@ -5764,37 +5764,37 @@
         <v>2.27</v>
       </c>
       <c r="M53">
-        <v>11.5928712</v>
+        <v>11.8201824</v>
       </c>
       <c r="N53">
-        <v>-9.322871200000002</v>
+        <v>-9.550182400000002</v>
       </c>
       <c r="O53">
-        <v>-1.86457424</v>
+        <v>-1.91003648</v>
       </c>
       <c r="P53">
-        <v>-7.458296960000001</v>
+        <v>-7.640145920000002</v>
       </c>
       <c r="Q53">
-        <v>-4.228296960000002</v>
+        <v>-4.410145920000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1307410428387712</v>
+        <v>0.1325106478979122</v>
       </c>
       <c r="T53">
-        <v>1.655659025607546</v>
+        <v>1.690151921974369</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03916199810794068</v>
+        <v>0.03840888275971105</v>
       </c>
       <c r="W53">
-        <v>0.2265656008461476</v>
+        <v>0.2267431854452601</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1958099905397034</v>
+        <v>0.1920444137985552</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1815115674225331</v>
+        <v>0.1834115674225331</v>
       </c>
       <c r="C54">
-        <v>-18.31849816281889</v>
+        <v>-19.67171001828878</v>
       </c>
       <c r="D54">
-        <v>28.18950183718112</v>
+        <v>27.80028998171123</v>
       </c>
       <c r="E54">
-        <v>35.42800000000001</v>
+        <v>36.39200000000001</v>
       </c>
       <c r="F54">
-        <v>50.12800000000001</v>
+        <v>51.09200000000001</v>
       </c>
       <c r="G54">
         <v>3.62</v>
@@ -5846,37 +5846,37 @@
         <v>2.27</v>
       </c>
       <c r="M54">
-        <v>11.8201824</v>
+        <v>12.0474936</v>
       </c>
       <c r="N54">
-        <v>-9.550182400000002</v>
+        <v>-9.777493600000001</v>
       </c>
       <c r="O54">
-        <v>-1.91003648</v>
+        <v>-1.95549872</v>
       </c>
       <c r="P54">
-        <v>-7.640145920000002</v>
+        <v>-7.821994880000001</v>
       </c>
       <c r="Q54">
-        <v>-4.410145920000001</v>
+        <v>-4.591994880000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1325106478979122</v>
+        <v>0.1343555552999955</v>
       </c>
       <c r="T54">
-        <v>1.690151921974369</v>
+        <v>1.726112601165313</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03840888275971105</v>
+        <v>0.03768418685858443</v>
       </c>
       <c r="W54">
-        <v>0.2267431854452601</v>
+        <v>0.2269140687387458</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1920444137985552</v>
+        <v>0.1884209342929221</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1834115674225331</v>
+        <v>0.1853115674225332</v>
       </c>
       <c r="C55">
-        <v>-19.67171001828878</v>
+        <v>-21.0143205660814</v>
       </c>
       <c r="D55">
-        <v>27.80028998171123</v>
+        <v>27.42167943391861</v>
       </c>
       <c r="E55">
-        <v>36.39200000000001</v>
+        <v>37.35600000000001</v>
       </c>
       <c r="F55">
-        <v>51.09200000000001</v>
+        <v>52.056</v>
       </c>
       <c r="G55">
         <v>3.62</v>
@@ -5928,37 +5928,37 @@
         <v>2.27</v>
       </c>
       <c r="M55">
-        <v>12.0474936</v>
+        <v>12.2748048</v>
       </c>
       <c r="N55">
-        <v>-9.777493600000001</v>
+        <v>-10.0048048</v>
       </c>
       <c r="O55">
-        <v>-1.95549872</v>
+        <v>-2.00096096</v>
       </c>
       <c r="P55">
-        <v>-7.821994880000001</v>
+        <v>-8.003843840000002</v>
       </c>
       <c r="Q55">
-        <v>-4.591994880000001</v>
+        <v>-4.773843840000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1343555552999955</v>
+        <v>0.1362806760673867</v>
       </c>
       <c r="T55">
-        <v>1.726112601165313</v>
+        <v>1.763636788147168</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03768418685858443</v>
+        <v>0.03698633154638841</v>
       </c>
       <c r="W55">
-        <v>0.2269140687387458</v>
+        <v>0.2270786230213616</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1884209342929221</v>
+        <v>0.1849316577319421</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1853115674225332</v>
+        <v>0.1872115674225331</v>
       </c>
       <c r="C56">
-        <v>-21.0143205660814</v>
+        <v>-22.34675712239768</v>
       </c>
       <c r="D56">
-        <v>27.42167943391861</v>
+        <v>27.05324287760233</v>
       </c>
       <c r="E56">
-        <v>37.35600000000001</v>
+        <v>38.32000000000001</v>
       </c>
       <c r="F56">
-        <v>52.056</v>
+        <v>53.02000000000001</v>
       </c>
       <c r="G56">
         <v>3.62</v>
@@ -6010,37 +6010,37 @@
         <v>2.27</v>
       </c>
       <c r="M56">
-        <v>12.2748048</v>
+        <v>12.502116</v>
       </c>
       <c r="N56">
-        <v>-10.0048048</v>
+        <v>-10.232116</v>
       </c>
       <c r="O56">
-        <v>-2.00096096</v>
+        <v>-2.046423200000001</v>
       </c>
       <c r="P56">
-        <v>-8.003843840000002</v>
+        <v>-8.185692800000002</v>
       </c>
       <c r="Q56">
-        <v>-4.773843840000001</v>
+        <v>-4.955692800000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1362806760673867</v>
+        <v>0.138291357757773</v>
       </c>
       <c r="T56">
-        <v>1.763636788147168</v>
+        <v>1.80282871677266</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03698633154638841</v>
+        <v>0.03631385279099954</v>
       </c>
       <c r="W56">
-        <v>0.2270786230213616</v>
+        <v>0.2272371935118823</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1849316577319421</v>
+        <v>0.1815692639549976</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1872115674225331</v>
+        <v>0.1891115674225332</v>
       </c>
       <c r="C57">
-        <v>-22.34675712239768</v>
+        <v>-23.66942434230112</v>
       </c>
       <c r="D57">
-        <v>27.05324287760233</v>
+        <v>26.69457565769888</v>
       </c>
       <c r="E57">
-        <v>38.32000000000001</v>
+        <v>39.28400000000001</v>
       </c>
       <c r="F57">
-        <v>53.02000000000001</v>
+        <v>53.98400000000001</v>
       </c>
       <c r="G57">
         <v>3.62</v>
@@ -6092,37 +6092,37 @@
         <v>2.27</v>
       </c>
       <c r="M57">
-        <v>12.502116</v>
+        <v>12.7294272</v>
       </c>
       <c r="N57">
-        <v>-10.232116</v>
+        <v>-10.4594272</v>
       </c>
       <c r="O57">
-        <v>-2.046423200000001</v>
+        <v>-2.091885440000001</v>
       </c>
       <c r="P57">
-        <v>-8.185692800000002</v>
+        <v>-8.367541760000003</v>
       </c>
       <c r="Q57">
-        <v>-4.955692800000001</v>
+        <v>-5.137541760000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.138291357757773</v>
+        <v>0.1403934340704497</v>
       </c>
       <c r="T57">
-        <v>1.80282871677266</v>
+        <v>1.843802096699312</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03631385279099954</v>
+        <v>0.03566539113401739</v>
       </c>
       <c r="W57">
-        <v>0.2272371935118823</v>
+        <v>0.2273901007705987</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1815692639549976</v>
+        <v>0.1783269556700869</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1891115674225332</v>
+        <v>0.1910115674225332</v>
       </c>
       <c r="C58">
-        <v>-23.66942434230112</v>
+        <v>-24.98270570224984</v>
       </c>
       <c r="D58">
-        <v>26.69457565769888</v>
+        <v>26.34529429775017</v>
       </c>
       <c r="E58">
-        <v>39.28400000000001</v>
+        <v>40.248</v>
       </c>
       <c r="F58">
-        <v>53.98400000000001</v>
+        <v>54.94800000000001</v>
       </c>
       <c r="G58">
         <v>3.62</v>
@@ -6174,37 +6174,37 @@
         <v>2.27</v>
       </c>
       <c r="M58">
-        <v>12.7294272</v>
+        <v>12.9567384</v>
       </c>
       <c r="N58">
-        <v>-10.4594272</v>
+        <v>-10.6867384</v>
       </c>
       <c r="O58">
-        <v>-2.091885440000001</v>
+        <v>-2.137347680000001</v>
       </c>
       <c r="P58">
-        <v>-8.367541760000003</v>
+        <v>-8.549390720000002</v>
       </c>
       <c r="Q58">
-        <v>-5.137541760000003</v>
+        <v>-5.319390720000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1403934340704497</v>
+        <v>0.1425932813744137</v>
       </c>
       <c r="T58">
-        <v>1.843802096699312</v>
+        <v>1.886681215227203</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03566539113401739</v>
+        <v>0.03503968251763113</v>
       </c>
       <c r="W58">
-        <v>0.2273901007705987</v>
+        <v>0.2275376428623426</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1783269556700869</v>
+        <v>0.1751984125881556</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1910115674225332</v>
+        <v>0.1929115674225332</v>
       </c>
       <c r="C59">
-        <v>-24.98270570224984</v>
+        <v>-26.28696486774398</v>
       </c>
       <c r="D59">
-        <v>26.34529429775017</v>
+        <v>26.00503513225603</v>
       </c>
       <c r="E59">
-        <v>40.248</v>
+        <v>41.21200000000002</v>
       </c>
       <c r="F59">
-        <v>54.94800000000001</v>
+        <v>55.91200000000001</v>
       </c>
       <c r="G59">
         <v>3.62</v>
@@ -6256,37 +6256,37 @@
         <v>2.27</v>
       </c>
       <c r="M59">
-        <v>12.9567384</v>
+        <v>13.1840496</v>
       </c>
       <c r="N59">
-        <v>-10.6867384</v>
+        <v>-10.9140496</v>
       </c>
       <c r="O59">
-        <v>-2.137347680000001</v>
+        <v>-2.182809920000001</v>
       </c>
       <c r="P59">
-        <v>-8.549390720000002</v>
+        <v>-8.731239680000003</v>
       </c>
       <c r="Q59">
-        <v>-5.319390720000001</v>
+        <v>-5.501239680000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1425932813744137</v>
+        <v>0.1448978833118997</v>
       </c>
       <c r="T59">
-        <v>1.886681215227203</v>
+        <v>1.931602196542136</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03503968251763113</v>
+        <v>0.03443555006043059</v>
       </c>
       <c r="W59">
-        <v>0.2275376428623426</v>
+        <v>0.2276800972957505</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1751984125881556</v>
+        <v>0.1721777503021529</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1929115674225331</v>
+        <v>0.1948115674225331</v>
       </c>
       <c r="C60">
-        <v>-26.28696486774396</v>
+        <v>-27.58254695634237</v>
       </c>
       <c r="D60">
-        <v>26.00503513225604</v>
+        <v>25.67345304365762</v>
       </c>
       <c r="E60">
-        <v>41.212</v>
+        <v>42.176</v>
       </c>
       <c r="F60">
-        <v>55.912</v>
+        <v>56.876</v>
       </c>
       <c r="G60">
         <v>3.62</v>
@@ -6338,37 +6338,37 @@
         <v>2.27</v>
       </c>
       <c r="M60">
-        <v>13.1840496</v>
+        <v>13.4113608</v>
       </c>
       <c r="N60">
-        <v>-10.9140496</v>
+        <v>-11.1413608</v>
       </c>
       <c r="O60">
-        <v>-2.18280992</v>
+        <v>-2.22827216</v>
       </c>
       <c r="P60">
-        <v>-8.73123968</v>
+        <v>-8.913088640000002</v>
       </c>
       <c r="Q60">
-        <v>-5.501239679999999</v>
+        <v>-5.683088640000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1448978833118997</v>
+        <v>0.1473149048560924</v>
       </c>
       <c r="T60">
-        <v>1.931602196542136</v>
+        <v>1.978714445238286</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0344355500604306</v>
+        <v>0.03385189666957585</v>
       </c>
       <c r="W60">
-        <v>0.2276800972957505</v>
+        <v>0.227817722765314</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.172177750302153</v>
+        <v>0.1692594833478792</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1948115674225331</v>
+        <v>0.1967115674225332</v>
       </c>
       <c r="C61">
-        <v>-27.58254695634237</v>
+        <v>-28.86977970526993</v>
       </c>
       <c r="D61">
-        <v>25.67345304365762</v>
+        <v>25.35022029473008</v>
       </c>
       <c r="E61">
-        <v>42.176</v>
+        <v>43.14</v>
       </c>
       <c r="F61">
-        <v>56.876</v>
+        <v>57.84</v>
       </c>
       <c r="G61">
         <v>3.62</v>
@@ -6420,37 +6420,37 @@
         <v>2.27</v>
       </c>
       <c r="M61">
-        <v>13.4113608</v>
+        <v>13.638672</v>
       </c>
       <c r="N61">
-        <v>-11.1413608</v>
+        <v>-11.368672</v>
       </c>
       <c r="O61">
-        <v>-2.22827216</v>
+        <v>-2.2737344</v>
       </c>
       <c r="P61">
-        <v>-8.913088640000002</v>
+        <v>-9.094937600000002</v>
       </c>
       <c r="Q61">
-        <v>-5.683088640000001</v>
+        <v>-5.864937600000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1473149048560924</v>
+        <v>0.1498527774774947</v>
       </c>
       <c r="T61">
-        <v>1.978714445238286</v>
+        <v>2.028182306369243</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03385189666957585</v>
+        <v>0.03328769839174957</v>
       </c>
       <c r="W61">
-        <v>0.227817722765314</v>
+        <v>0.2279507607192255</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1692594833478792</v>
+        <v>0.1664384919587478</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1967115674225332</v>
+        <v>0.1986115674225331</v>
       </c>
       <c r="C62">
-        <v>-28.86977970526993</v>
+        <v>-30.14897455191923</v>
       </c>
       <c r="D62">
-        <v>25.35022029473008</v>
+        <v>25.03502544808077</v>
       </c>
       <c r="E62">
-        <v>43.14</v>
+        <v>44.104</v>
       </c>
       <c r="F62">
-        <v>57.84</v>
+        <v>58.804</v>
       </c>
       <c r="G62">
         <v>3.62</v>
@@ -6502,37 +6502,37 @@
         <v>2.27</v>
       </c>
       <c r="M62">
-        <v>13.638672</v>
+        <v>13.8659832</v>
       </c>
       <c r="N62">
-        <v>-11.368672</v>
+        <v>-11.5959832</v>
       </c>
       <c r="O62">
-        <v>-2.2737344</v>
+        <v>-2.31919664</v>
       </c>
       <c r="P62">
-        <v>-9.094937600000002</v>
+        <v>-9.276786560000001</v>
       </c>
       <c r="Q62">
-        <v>-5.864937600000001</v>
+        <v>-6.046786560000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1498527774774947</v>
+        <v>0.1525207974128151</v>
       </c>
       <c r="T62">
-        <v>2.028182306369243</v>
+        <v>2.080186980891531</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03328769839174957</v>
+        <v>0.03274199841811434</v>
       </c>
       <c r="W62">
-        <v>0.2279507607192255</v>
+        <v>0.2280794367730087</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1664384919587478</v>
+        <v>0.1637099920905717</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1986115674225331</v>
+        <v>0.2005115674225332</v>
       </c>
       <c r="C63">
-        <v>-30.14897455191923</v>
+        <v>-31.42042763473525</v>
       </c>
       <c r="D63">
-        <v>25.03502544808077</v>
+        <v>24.72757236526475</v>
       </c>
       <c r="E63">
-        <v>44.104</v>
+        <v>45.068</v>
       </c>
       <c r="F63">
-        <v>58.804</v>
+        <v>59.768</v>
       </c>
       <c r="G63">
         <v>3.62</v>
@@ -6584,37 +6584,37 @@
         <v>2.27</v>
       </c>
       <c r="M63">
-        <v>13.8659832</v>
+        <v>14.0932944</v>
       </c>
       <c r="N63">
-        <v>-11.5959832</v>
+        <v>-11.8232944</v>
       </c>
       <c r="O63">
-        <v>-2.31919664</v>
+        <v>-2.36465888</v>
       </c>
       <c r="P63">
-        <v>-9.276786560000001</v>
+        <v>-9.458635520000001</v>
       </c>
       <c r="Q63">
-        <v>-6.046786560000001</v>
+        <v>-6.228635520000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1525207974128151</v>
+        <v>0.1553292394499944</v>
       </c>
       <c r="T63">
-        <v>2.080186980891531</v>
+        <v>2.134928743546572</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03274199841811434</v>
+        <v>0.03221390166943507</v>
       </c>
       <c r="W63">
-        <v>0.2280794367730087</v>
+        <v>0.2282039619863472</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1637099920905717</v>
+        <v>0.1610695083471754</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2005115674225332</v>
+        <v>0.2024115674225332</v>
       </c>
       <c r="C64">
-        <v>-31.42042763473525</v>
+        <v>-32.68442072124364</v>
       </c>
       <c r="D64">
-        <v>24.72757236526475</v>
+        <v>24.42757927875637</v>
       </c>
       <c r="E64">
-        <v>45.068</v>
+        <v>46.03200000000001</v>
       </c>
       <c r="F64">
-        <v>59.768</v>
+        <v>60.73200000000001</v>
       </c>
       <c r="G64">
         <v>3.62</v>
@@ -6666,37 +6666,37 @@
         <v>2.27</v>
       </c>
       <c r="M64">
-        <v>14.0932944</v>
+        <v>14.3206056</v>
       </c>
       <c r="N64">
-        <v>-11.8232944</v>
+        <v>-12.0506056</v>
       </c>
       <c r="O64">
-        <v>-2.36465888</v>
+        <v>-2.410121120000001</v>
       </c>
       <c r="P64">
-        <v>-9.458635520000001</v>
+        <v>-9.640484480000001</v>
       </c>
       <c r="Q64">
-        <v>-6.228635520000001</v>
+        <v>-6.410484480000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1553292394499944</v>
+        <v>0.1582894891648591</v>
       </c>
       <c r="T64">
-        <v>2.134928743546572</v>
+        <v>2.192629520399182</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03221390166943507</v>
+        <v>0.03170256989690436</v>
       </c>
       <c r="W64">
-        <v>0.2282039619863472</v>
+        <v>0.22832453401831</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1610695083471754</v>
+        <v>0.1585128494845217</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2024115674225332</v>
+        <v>0.2043115674225332</v>
       </c>
       <c r="C65">
-        <v>-32.68442072124364</v>
+        <v>-33.94122206933655</v>
       </c>
       <c r="D65">
-        <v>24.42757927875637</v>
+        <v>24.13477793066346</v>
       </c>
       <c r="E65">
-        <v>46.03200000000001</v>
+        <v>46.99600000000001</v>
       </c>
       <c r="F65">
-        <v>60.73200000000001</v>
+        <v>61.69600000000001</v>
       </c>
       <c r="G65">
         <v>3.62</v>
@@ -6748,37 +6748,37 @@
         <v>2.27</v>
       </c>
       <c r="M65">
-        <v>14.3206056</v>
+        <v>14.5479168</v>
       </c>
       <c r="N65">
-        <v>-12.0506056</v>
+        <v>-12.2779168</v>
       </c>
       <c r="O65">
-        <v>-2.410121120000001</v>
+        <v>-2.45558336</v>
       </c>
       <c r="P65">
-        <v>-9.640484480000001</v>
+        <v>-9.822333440000001</v>
       </c>
       <c r="Q65">
-        <v>-6.410484480000001</v>
+        <v>-6.592333440000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1582894891648591</v>
+        <v>0.1614141971972163</v>
       </c>
       <c r="T65">
-        <v>2.192629520399182</v>
+        <v>2.253535895965826</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03170256989690436</v>
+        <v>0.03120721724226523</v>
       </c>
       <c r="W65">
-        <v>0.22832453401831</v>
+        <v>0.2284413381742739</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1585128494845217</v>
+        <v>0.1560360862113261</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2043115674225332</v>
+        <v>0.2062115674225332</v>
       </c>
       <c r="C66">
-        <v>-33.94122206933655</v>
+        <v>-35.19108722734895</v>
       </c>
       <c r="D66">
-        <v>24.13477793066346</v>
+        <v>23.84891277265105</v>
       </c>
       <c r="E66">
-        <v>46.99600000000001</v>
+        <v>47.96000000000001</v>
       </c>
       <c r="F66">
-        <v>61.69600000000001</v>
+        <v>62.66</v>
       </c>
       <c r="G66">
         <v>3.62</v>
@@ -6830,37 +6830,37 @@
         <v>2.27</v>
       </c>
       <c r="M66">
-        <v>14.5479168</v>
+        <v>14.775228</v>
       </c>
       <c r="N66">
-        <v>-12.2779168</v>
+        <v>-12.505228</v>
       </c>
       <c r="O66">
-        <v>-2.45558336</v>
+        <v>-2.501045600000001</v>
       </c>
       <c r="P66">
-        <v>-9.822333440000001</v>
+        <v>-10.0041824</v>
       </c>
       <c r="Q66">
-        <v>-6.592333440000001</v>
+        <v>-6.774182400000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1614141971972163</v>
+        <v>0.1647174599742796</v>
       </c>
       <c r="T66">
-        <v>2.253535895965826</v>
+        <v>2.317922635850564</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03120721724226523</v>
+        <v>0.03072710620776884</v>
       </c>
       <c r="W66">
-        <v>0.2284413381742739</v>
+        <v>0.2285545483562081</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1560360862113261</v>
+        <v>0.1536355310388442</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2062115674225332</v>
+        <v>0.2081115674225332</v>
       </c>
       <c r="C67">
-        <v>-35.19108722734895</v>
+        <v>-36.43425977794159</v>
       </c>
       <c r="D67">
-        <v>23.84891277265105</v>
+        <v>23.56974022205842</v>
       </c>
       <c r="E67">
-        <v>47.96000000000001</v>
+        <v>48.92400000000001</v>
       </c>
       <c r="F67">
-        <v>62.66</v>
+        <v>63.62400000000001</v>
       </c>
       <c r="G67">
         <v>3.62</v>
@@ -6912,37 +6912,37 @@
         <v>2.27</v>
       </c>
       <c r="M67">
-        <v>14.775228</v>
+        <v>15.0025392</v>
       </c>
       <c r="N67">
-        <v>-12.505228</v>
+        <v>-12.7325392</v>
       </c>
       <c r="O67">
-        <v>-2.501045600000001</v>
+        <v>-2.546507840000001</v>
       </c>
       <c r="P67">
-        <v>-10.0041824</v>
+        <v>-10.18603136</v>
       </c>
       <c r="Q67">
-        <v>-6.774182400000001</v>
+        <v>-6.956031360000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1647174599742796</v>
+        <v>0.1682150323264643</v>
       </c>
       <c r="T67">
-        <v>2.317922635850564</v>
+        <v>2.386096831022639</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03072710620776884</v>
+        <v>0.03026154399249961</v>
       </c>
       <c r="W67">
-        <v>0.2285545483562081</v>
+        <v>0.2286643279265686</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1536355310388442</v>
+        <v>0.151307719962498</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2081115674225332</v>
+        <v>0.2100115674225332</v>
       </c>
       <c r="C68">
-        <v>-36.43425977794159</v>
+        <v>-37.67097203034145</v>
       </c>
       <c r="D68">
-        <v>23.56974022205842</v>
+        <v>23.29702796965855</v>
       </c>
       <c r="E68">
-        <v>48.92400000000001</v>
+        <v>49.88800000000001</v>
       </c>
       <c r="F68">
-        <v>63.62400000000001</v>
+        <v>64.58800000000001</v>
       </c>
       <c r="G68">
         <v>3.62</v>
@@ -6994,37 +6994,37 @@
         <v>2.27</v>
       </c>
       <c r="M68">
-        <v>15.0025392</v>
+        <v>15.2298504</v>
       </c>
       <c r="N68">
-        <v>-12.7325392</v>
+        <v>-12.9598504</v>
       </c>
       <c r="O68">
-        <v>-2.546507840000001</v>
+        <v>-2.591970080000001</v>
       </c>
       <c r="P68">
-        <v>-10.18603136</v>
+        <v>-10.36788032</v>
       </c>
       <c r="Q68">
-        <v>-6.956031360000003</v>
+        <v>-7.137880320000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1682150323264643</v>
+        <v>0.1719245787605996</v>
       </c>
       <c r="T68">
-        <v>2.386096831022639</v>
+        <v>2.458402795599083</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03026154399249961</v>
+        <v>0.02980987915679066</v>
       </c>
       <c r="W68">
-        <v>0.2286643279265686</v>
+        <v>0.2287708304948288</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.151307719962498</v>
+        <v>0.1490493957839533</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2100115674225332</v>
+        <v>0.2119115674225332</v>
       </c>
       <c r="C69">
-        <v>-37.67097203034145</v>
+        <v>-38.90144566507489</v>
       </c>
       <c r="D69">
-        <v>23.29702796965855</v>
+        <v>23.03055433492511</v>
       </c>
       <c r="E69">
-        <v>49.88800000000001</v>
+        <v>50.852</v>
       </c>
       <c r="F69">
-        <v>64.58800000000001</v>
+        <v>65.55200000000001</v>
       </c>
       <c r="G69">
         <v>3.62</v>
@@ -7076,37 +7076,37 @@
         <v>2.27</v>
       </c>
       <c r="M69">
-        <v>15.2298504</v>
+        <v>15.4571616</v>
       </c>
       <c r="N69">
-        <v>-12.9598504</v>
+        <v>-13.1871616</v>
       </c>
       <c r="O69">
-        <v>-2.591970080000001</v>
+        <v>-2.637432320000001</v>
       </c>
       <c r="P69">
-        <v>-10.36788032</v>
+        <v>-10.54972928</v>
       </c>
       <c r="Q69">
-        <v>-7.137880320000001</v>
+        <v>-7.319729280000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1719245787605996</v>
+        <v>0.1758659718468684</v>
       </c>
       <c r="T69">
-        <v>2.458402795599083</v>
+        <v>2.535227882961554</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02980987915679066</v>
+        <v>0.02937149858095551</v>
       </c>
       <c r="W69">
-        <v>0.2287708304948288</v>
+        <v>0.2288742006346107</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1490493957839533</v>
+        <v>0.1468574929047775</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2119115674225332</v>
+        <v>0.2138115674225332</v>
       </c>
       <c r="C70">
-        <v>-38.90144566507489</v>
+        <v>-40.12589233495393</v>
       </c>
       <c r="D70">
-        <v>23.03055433492511</v>
+        <v>22.77010766504607</v>
       </c>
       <c r="E70">
-        <v>50.852</v>
+        <v>51.816</v>
       </c>
       <c r="F70">
-        <v>65.55200000000001</v>
+        <v>66.51600000000001</v>
       </c>
       <c r="G70">
         <v>3.62</v>
@@ -7158,37 +7158,37 @@
         <v>2.27</v>
       </c>
       <c r="M70">
-        <v>15.4571616</v>
+        <v>15.6844728</v>
       </c>
       <c r="N70">
-        <v>-13.1871616</v>
+        <v>-13.4144728</v>
       </c>
       <c r="O70">
-        <v>-2.637432320000001</v>
+        <v>-2.682894560000001</v>
       </c>
       <c r="P70">
-        <v>-10.54972928</v>
+        <v>-10.73157824</v>
       </c>
       <c r="Q70">
-        <v>-7.319729280000002</v>
+        <v>-7.501578240000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1758659718468684</v>
+        <v>0.1800616483580577</v>
       </c>
       <c r="T70">
-        <v>2.535227882961554</v>
+        <v>2.617009427573218</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02937149858095551</v>
+        <v>0.02894582468847789</v>
       </c>
       <c r="W70">
-        <v>0.2288742006346107</v>
+        <v>0.2289745745384569</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1468574929047775</v>
+        <v>0.1447291234423894</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2138115674225332</v>
+        <v>0.2157115674225331</v>
       </c>
       <c r="C71">
-        <v>-40.12589233495393</v>
+        <v>-41.34451422574022</v>
       </c>
       <c r="D71">
-        <v>22.77010766504607</v>
+        <v>22.51548577425978</v>
       </c>
       <c r="E71">
-        <v>51.816</v>
+        <v>52.78</v>
       </c>
       <c r="F71">
-        <v>66.51600000000001</v>
+        <v>67.48</v>
       </c>
       <c r="G71">
         <v>3.62</v>
@@ -7240,37 +7240,37 @@
         <v>2.27</v>
       </c>
       <c r="M71">
-        <v>15.6844728</v>
+        <v>15.911784</v>
       </c>
       <c r="N71">
-        <v>-13.4144728</v>
+        <v>-13.641784</v>
       </c>
       <c r="O71">
-        <v>-2.682894560000001</v>
+        <v>-2.7283568</v>
       </c>
       <c r="P71">
-        <v>-10.73157824</v>
+        <v>-10.9134272</v>
       </c>
       <c r="Q71">
-        <v>-7.501578240000001</v>
+        <v>-7.683427200000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1800616483580577</v>
+        <v>0.1845370366366596</v>
       </c>
       <c r="T71">
-        <v>2.617009427573218</v>
+        <v>2.704243075158991</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02894582468847789</v>
+        <v>0.02853231290721393</v>
       </c>
       <c r="W71">
-        <v>0.2289745745384569</v>
+        <v>0.229072080616479</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1447291234423894</v>
+        <v>0.1426615645360696</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2157115674225331</v>
+        <v>0.2176115674225332</v>
       </c>
       <c r="C72">
-        <v>-41.34451422574022</v>
+        <v>-42.55750457960789</v>
       </c>
       <c r="D72">
-        <v>22.51548577425978</v>
+        <v>22.26649542039212</v>
       </c>
       <c r="E72">
-        <v>52.78</v>
+        <v>53.74400000000001</v>
       </c>
       <c r="F72">
-        <v>67.48</v>
+        <v>68.44400000000002</v>
       </c>
       <c r="G72">
         <v>3.62</v>
@@ -7322,37 +7322,37 @@
         <v>2.27</v>
       </c>
       <c r="M72">
-        <v>15.911784</v>
+        <v>16.1390952</v>
       </c>
       <c r="N72">
-        <v>-13.641784</v>
+        <v>-13.8690952</v>
       </c>
       <c r="O72">
-        <v>-2.7283568</v>
+        <v>-2.773819040000001</v>
       </c>
       <c r="P72">
-        <v>-10.9134272</v>
+        <v>-11.09527616</v>
       </c>
       <c r="Q72">
-        <v>-7.683427200000001</v>
+        <v>-7.865276160000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1845370366366596</v>
+        <v>0.1893210723827513</v>
       </c>
       <c r="T72">
-        <v>2.704243075158991</v>
+        <v>2.79749283637137</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02853231290721393</v>
+        <v>0.02813044934514049</v>
       </c>
       <c r="W72">
-        <v>0.229072080616479</v>
+        <v>0.2291668400444159</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1426615645360696</v>
+        <v>0.1406522467257024</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2176115674225331</v>
+        <v>0.2195115674225332</v>
       </c>
       <c r="C73">
-        <v>-42.55750457960788</v>
+        <v>-43.76504818425362</v>
       </c>
       <c r="D73">
-        <v>22.26649542039212</v>
+        <v>22.02295181574638</v>
       </c>
       <c r="E73">
-        <v>53.744</v>
+        <v>54.708</v>
       </c>
       <c r="F73">
-        <v>68.444</v>
+        <v>69.408</v>
       </c>
       <c r="G73">
         <v>3.62</v>
@@ -7404,37 +7404,37 @@
         <v>2.27</v>
       </c>
       <c r="M73">
-        <v>16.1390952</v>
+        <v>16.3664064</v>
       </c>
       <c r="N73">
-        <v>-13.8690952</v>
+        <v>-14.0964064</v>
       </c>
       <c r="O73">
-        <v>-2.77381904</v>
+        <v>-2.819281280000001</v>
       </c>
       <c r="P73">
-        <v>-11.09527616</v>
+        <v>-11.27712512</v>
       </c>
       <c r="Q73">
-        <v>-7.865276160000001</v>
+        <v>-8.047125120000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1893210723827513</v>
+        <v>0.1944468249678495</v>
       </c>
       <c r="T73">
-        <v>2.797492836371369</v>
+        <v>2.897403294813204</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02813044934514049</v>
+        <v>0.02773974865979131</v>
       </c>
       <c r="W73">
-        <v>0.2291668400444159</v>
+        <v>0.2292589672660212</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1406522467257024</v>
+        <v>0.1386987432989565</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2195115674225332</v>
+        <v>0.2214115674225332</v>
       </c>
       <c r="C74">
-        <v>-43.76504818425362</v>
+        <v>-44.96732183025576</v>
       </c>
       <c r="D74">
-        <v>22.02295181574638</v>
+        <v>21.78467816974424</v>
       </c>
       <c r="E74">
-        <v>54.708</v>
+        <v>55.672</v>
       </c>
       <c r="F74">
-        <v>69.408</v>
+        <v>70.372</v>
       </c>
       <c r="G74">
         <v>3.62</v>
@@ -7486,37 +7486,37 @@
         <v>2.27</v>
       </c>
       <c r="M74">
-        <v>16.3664064</v>
+        <v>16.5937176</v>
       </c>
       <c r="N74">
-        <v>-14.0964064</v>
+        <v>-14.3237176</v>
       </c>
       <c r="O74">
-        <v>-2.819281280000001</v>
+        <v>-2.864743520000001</v>
       </c>
       <c r="P74">
-        <v>-11.27712512</v>
+        <v>-11.45897408</v>
       </c>
       <c r="Q74">
-        <v>-8.047125120000002</v>
+        <v>-8.22897408</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1944468249678495</v>
+        <v>0.1999522629296218</v>
       </c>
       <c r="T74">
-        <v>2.897403294813204</v>
+        <v>3.004714527954434</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02773974865979131</v>
+        <v>0.02735975210280787</v>
       </c>
       <c r="W74">
-        <v>0.2292589672660212</v>
+        <v>0.2293485704541579</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1386987432989565</v>
+        <v>0.1367987605140393</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2214115674225332</v>
+        <v>0.2233115674225332</v>
       </c>
       <c r="C75">
-        <v>-44.96732183025576</v>
+        <v>-46.16449473906114</v>
       </c>
       <c r="D75">
-        <v>21.78467816974424</v>
+        <v>21.55150526093886</v>
       </c>
       <c r="E75">
-        <v>55.672</v>
+        <v>56.636</v>
       </c>
       <c r="F75">
-        <v>70.372</v>
+        <v>71.336</v>
       </c>
       <c r="G75">
         <v>3.62</v>
@@ -7568,37 +7568,37 @@
         <v>2.27</v>
       </c>
       <c r="M75">
-        <v>16.5937176</v>
+        <v>16.8210288</v>
       </c>
       <c r="N75">
-        <v>-14.3237176</v>
+        <v>-14.5510288</v>
       </c>
       <c r="O75">
-        <v>-2.864743520000001</v>
+        <v>-2.91020576</v>
       </c>
       <c r="P75">
-        <v>-11.45897408</v>
+        <v>-11.64082304</v>
       </c>
       <c r="Q75">
-        <v>-8.22897408</v>
+        <v>-8.41082304</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1999522629296218</v>
+        <v>0.2058811961192226</v>
       </c>
       <c r="T75">
-        <v>3.004714527954434</v>
+        <v>3.120280471337296</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02735975210280787</v>
+        <v>0.0269900257230402</v>
       </c>
       <c r="W75">
-        <v>0.2293485704541579</v>
+        <v>0.2294357519345071</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1367987605140393</v>
+        <v>0.1349501286152009</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2233115674225332</v>
+        <v>0.2252115674225331</v>
       </c>
       <c r="C76">
-        <v>-46.16449473906114</v>
+        <v>-47.35672896377726</v>
       </c>
       <c r="D76">
-        <v>21.55150526093886</v>
+        <v>21.32327103622275</v>
       </c>
       <c r="E76">
-        <v>56.636</v>
+        <v>57.60000000000001</v>
       </c>
       <c r="F76">
-        <v>71.336</v>
+        <v>72.30000000000001</v>
       </c>
       <c r="G76">
         <v>3.62</v>
@@ -7650,37 +7650,37 @@
         <v>2.27</v>
       </c>
       <c r="M76">
-        <v>16.8210288</v>
+        <v>17.04834</v>
       </c>
       <c r="N76">
-        <v>-14.5510288</v>
+        <v>-14.77834</v>
       </c>
       <c r="O76">
-        <v>-2.91020576</v>
+        <v>-2.955668000000001</v>
       </c>
       <c r="P76">
-        <v>-11.64082304</v>
+        <v>-11.822672</v>
       </c>
       <c r="Q76">
-        <v>-8.41082304</v>
+        <v>-8.592672000000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2058811961192226</v>
+        <v>0.2122844439639915</v>
       </c>
       <c r="T76">
-        <v>3.120280471337296</v>
+        <v>3.245091690190789</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0269900257230402</v>
+        <v>0.02663015871339966</v>
       </c>
       <c r="W76">
-        <v>0.2294357519345071</v>
+        <v>0.2295206085753804</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1349501286152009</v>
+        <v>0.1331507935669982</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2252115674225331</v>
+        <v>0.2271115674225332</v>
       </c>
       <c r="C77">
-        <v>-47.35672896377726</v>
+        <v>-48.54417976476454</v>
       </c>
       <c r="D77">
-        <v>21.32327103622275</v>
+        <v>21.09982023523547</v>
       </c>
       <c r="E77">
-        <v>57.60000000000001</v>
+        <v>58.56400000000001</v>
       </c>
       <c r="F77">
-        <v>72.30000000000001</v>
+        <v>73.26400000000001</v>
       </c>
       <c r="G77">
         <v>3.62</v>
@@ -7732,37 +7732,37 @@
         <v>2.27</v>
       </c>
       <c r="M77">
-        <v>17.04834</v>
+        <v>17.2756512</v>
       </c>
       <c r="N77">
-        <v>-14.77834</v>
+        <v>-15.0056512</v>
       </c>
       <c r="O77">
-        <v>-2.955668000000001</v>
+        <v>-3.001130240000001</v>
       </c>
       <c r="P77">
-        <v>-11.822672</v>
+        <v>-12.00452096</v>
       </c>
       <c r="Q77">
-        <v>-8.592672000000002</v>
+        <v>-8.774520960000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2122844439639915</v>
+        <v>0.2192212957958245</v>
       </c>
       <c r="T77">
-        <v>3.245091690190789</v>
+        <v>3.380303843948738</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02663015871339966</v>
+        <v>0.02627976188822335</v>
       </c>
       <c r="W77">
-        <v>0.2295206085753804</v>
+        <v>0.229603232146757</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1331507935669982</v>
+        <v>0.1313988094411167</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2271115674225332</v>
+        <v>0.2290115674225331</v>
       </c>
       <c r="C78">
-        <v>-48.54417976476454</v>
+        <v>-49.72699596185808</v>
       </c>
       <c r="D78">
-        <v>21.09982023523547</v>
+        <v>20.88100403814193</v>
       </c>
       <c r="E78">
-        <v>58.56400000000001</v>
+        <v>59.52800000000001</v>
       </c>
       <c r="F78">
-        <v>73.26400000000001</v>
+        <v>74.22800000000001</v>
       </c>
       <c r="G78">
         <v>3.62</v>
@@ -7814,37 +7814,37 @@
         <v>2.27</v>
       </c>
       <c r="M78">
-        <v>17.2756512</v>
+        <v>17.5029624</v>
       </c>
       <c r="N78">
-        <v>-15.0056512</v>
+        <v>-15.2329624</v>
       </c>
       <c r="O78">
-        <v>-3.001130240000001</v>
+        <v>-3.046592480000001</v>
       </c>
       <c r="P78">
-        <v>-12.00452096</v>
+        <v>-12.18636992</v>
       </c>
       <c r="Q78">
-        <v>-8.774520960000002</v>
+        <v>-8.95636992</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2192212957958245</v>
+        <v>0.2267613521347734</v>
       </c>
       <c r="T78">
-        <v>3.380303843948738</v>
+        <v>3.527273576294336</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02627976188822335</v>
+        <v>0.02593846627928538</v>
       </c>
       <c r="W78">
-        <v>0.229603232146757</v>
+        <v>0.2296837096513445</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1313988094411167</v>
+        <v>0.1296923313964269</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2290115674225331</v>
+        <v>0.2309115674225332</v>
       </c>
       <c r="C79">
-        <v>-49.72699596185808</v>
+        <v>-50.90532026489804</v>
       </c>
       <c r="D79">
-        <v>20.88100403814193</v>
+        <v>20.66667973510197</v>
       </c>
       <c r="E79">
-        <v>59.52800000000001</v>
+        <v>60.492</v>
       </c>
       <c r="F79">
-        <v>74.22800000000001</v>
+        <v>75.19200000000001</v>
       </c>
       <c r="G79">
         <v>3.62</v>
@@ -7896,37 +7896,37 @@
         <v>2.27</v>
       </c>
       <c r="M79">
-        <v>17.5029624</v>
+        <v>17.7302736</v>
       </c>
       <c r="N79">
-        <v>-15.2329624</v>
+        <v>-15.4602736</v>
       </c>
       <c r="O79">
-        <v>-3.046592480000001</v>
+        <v>-3.092054720000001</v>
       </c>
       <c r="P79">
-        <v>-12.18636992</v>
+        <v>-12.36821888</v>
       </c>
       <c r="Q79">
-        <v>-8.95636992</v>
+        <v>-9.138218880000004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2267613521347734</v>
+        <v>0.2349868681408994</v>
       </c>
       <c r="T79">
-        <v>3.527273576294336</v>
+        <v>3.687604193398624</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02593846627928538</v>
+        <v>0.02560592183980736</v>
       </c>
       <c r="W79">
-        <v>0.2296837096513445</v>
+        <v>0.2297621236301734</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1296923313964269</v>
+        <v>0.1280296091990368</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2309115674225332</v>
+        <v>0.2328115674225331</v>
       </c>
       <c r="C80">
-        <v>-50.90532026489804</v>
+        <v>-52.07928958411119</v>
       </c>
       <c r="D80">
-        <v>20.66667973510197</v>
+        <v>20.45671041588881</v>
       </c>
       <c r="E80">
-        <v>60.492</v>
+        <v>61.456</v>
       </c>
       <c r="F80">
-        <v>75.19200000000001</v>
+        <v>76.15600000000001</v>
       </c>
       <c r="G80">
         <v>3.62</v>
@@ -7978,37 +7978,37 @@
         <v>2.27</v>
       </c>
       <c r="M80">
-        <v>17.7302736</v>
+        <v>17.9575848</v>
       </c>
       <c r="N80">
-        <v>-15.4602736</v>
+        <v>-15.6875848</v>
       </c>
       <c r="O80">
-        <v>-3.092054720000001</v>
+        <v>-3.137516960000001</v>
       </c>
       <c r="P80">
-        <v>-12.36821888</v>
+        <v>-12.55006784</v>
       </c>
       <c r="Q80">
-        <v>-9.138218880000004</v>
+        <v>-9.320067840000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2349868681408994</v>
+        <v>0.2439957666237995</v>
       </c>
       <c r="T80">
-        <v>3.687604193398624</v>
+        <v>3.863204393084273</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02560592183980736</v>
+        <v>0.02528179624689841</v>
       </c>
       <c r="W80">
-        <v>0.2297621236301734</v>
+        <v>0.2298385524449814</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1280296091990368</v>
+        <v>0.1264089812344921</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2328115674225331</v>
+        <v>0.2347115674225332</v>
       </c>
       <c r="C81">
-        <v>-52.07928958411119</v>
+        <v>-53.24903532176236</v>
       </c>
       <c r="D81">
-        <v>20.45671041588881</v>
+        <v>20.25096467823764</v>
       </c>
       <c r="E81">
-        <v>61.456</v>
+        <v>62.42</v>
       </c>
       <c r="F81">
-        <v>76.15600000000001</v>
+        <v>77.12</v>
       </c>
       <c r="G81">
         <v>3.62</v>
@@ -8060,37 +8060,37 @@
         <v>2.27</v>
       </c>
       <c r="M81">
-        <v>17.9575848</v>
+        <v>18.184896</v>
       </c>
       <c r="N81">
-        <v>-15.6875848</v>
+        <v>-15.914896</v>
       </c>
       <c r="O81">
-        <v>-3.137516960000001</v>
+        <v>-3.182979200000001</v>
       </c>
       <c r="P81">
-        <v>-12.55006784</v>
+        <v>-12.7319168</v>
       </c>
       <c r="Q81">
-        <v>-9.320067840000002</v>
+        <v>-9.501916800000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2439957666237995</v>
+        <v>0.2539055549549893</v>
       </c>
       <c r="T81">
-        <v>3.863204393084273</v>
+        <v>4.056364612738486</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02528179624689841</v>
+        <v>0.02496577379381218</v>
       </c>
       <c r="W81">
-        <v>0.2298385524449814</v>
+        <v>0.2299130705394191</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1264089812344921</v>
+        <v>0.1248288689690609</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2347115674225332</v>
+        <v>0.2366115674225331</v>
       </c>
       <c r="C82">
-        <v>-53.24903532176236</v>
+        <v>-54.41468364638122</v>
       </c>
       <c r="D82">
-        <v>20.25096467823764</v>
+        <v>20.04931635361878</v>
       </c>
       <c r="E82">
-        <v>62.42</v>
+        <v>63.384</v>
       </c>
       <c r="F82">
-        <v>77.12</v>
+        <v>78.084</v>
       </c>
       <c r="G82">
         <v>3.62</v>
@@ -8142,37 +8142,37 @@
         <v>2.27</v>
       </c>
       <c r="M82">
-        <v>18.184896</v>
+        <v>18.4122072</v>
       </c>
       <c r="N82">
-        <v>-15.914896</v>
+        <v>-16.1422072</v>
       </c>
       <c r="O82">
-        <v>-3.182979200000001</v>
+        <v>-3.228441440000001</v>
       </c>
       <c r="P82">
-        <v>-12.7319168</v>
+        <v>-12.91376576</v>
       </c>
       <c r="Q82">
-        <v>-9.501916800000002</v>
+        <v>-9.68376576</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2539055549549893</v>
+        <v>0.2648584788999889</v>
       </c>
       <c r="T82">
-        <v>4.056364612738486</v>
+        <v>4.269857487093144</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02496577379381218</v>
+        <v>0.02465755436425895</v>
       </c>
       <c r="W82">
-        <v>0.2299130705394191</v>
+        <v>0.2299857486809077</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1248288689690609</v>
+        <v>0.1232877718212947</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2366115674225331</v>
+        <v>0.2385115674225332</v>
       </c>
       <c r="C83">
-        <v>-54.41468364638122</v>
+        <v>-55.57635575076692</v>
       </c>
       <c r="D83">
-        <v>20.04931635361878</v>
+        <v>19.8516442492331</v>
       </c>
       <c r="E83">
-        <v>63.384</v>
+        <v>64.34800000000001</v>
       </c>
       <c r="F83">
-        <v>78.084</v>
+        <v>79.04800000000002</v>
       </c>
       <c r="G83">
         <v>3.62</v>
@@ -8224,37 +8224,37 @@
         <v>2.27</v>
       </c>
       <c r="M83">
-        <v>18.4122072</v>
+        <v>18.6395184</v>
       </c>
       <c r="N83">
-        <v>-16.1422072</v>
+        <v>-16.3695184</v>
       </c>
       <c r="O83">
-        <v>-3.228441440000001</v>
+        <v>-3.273903680000001</v>
       </c>
       <c r="P83">
-        <v>-12.91376576</v>
+        <v>-13.09561472</v>
       </c>
       <c r="Q83">
-        <v>-9.68376576</v>
+        <v>-9.865614720000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2648584788999889</v>
+        <v>0.2770283943944327</v>
       </c>
       <c r="T83">
-        <v>4.269857487093144</v>
+        <v>4.507071791931652</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02465755436425895</v>
+        <v>0.02435685248176798</v>
       </c>
       <c r="W83">
-        <v>0.2299857486809077</v>
+        <v>0.2300566541847991</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1232877718212947</v>
+        <v>0.1217842624088399</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2385115674225332</v>
+        <v>0.2404115674225332</v>
       </c>
       <c r="C84">
-        <v>-55.57635575076692</v>
+        <v>-56.73416809487928</v>
       </c>
       <c r="D84">
-        <v>19.8516442492331</v>
+        <v>19.65783190512073</v>
       </c>
       <c r="E84">
-        <v>64.34800000000001</v>
+        <v>65.31200000000001</v>
       </c>
       <c r="F84">
-        <v>79.04800000000002</v>
+        <v>80.01200000000001</v>
       </c>
       <c r="G84">
         <v>3.62</v>
@@ -8306,37 +8306,37 @@
         <v>2.27</v>
       </c>
       <c r="M84">
-        <v>18.6395184</v>
+        <v>18.8668296</v>
       </c>
       <c r="N84">
-        <v>-16.3695184</v>
+        <v>-16.5968296</v>
       </c>
       <c r="O84">
-        <v>-3.273903680000001</v>
+        <v>-3.319365920000001</v>
       </c>
       <c r="P84">
-        <v>-13.09561472</v>
+        <v>-13.27746368</v>
       </c>
       <c r="Q84">
-        <v>-9.865614720000004</v>
+        <v>-10.04746368</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2770283943944327</v>
+        <v>0.2906300646529288</v>
       </c>
       <c r="T84">
-        <v>4.507071791931652</v>
+        <v>4.77219366204528</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02435685248176798</v>
+        <v>0.02406339642777078</v>
       </c>
       <c r="W84">
-        <v>0.2300566541847991</v>
+        <v>0.2301258511223317</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1217842624088399</v>
+        <v>0.1203169821388539</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2404115674225332</v>
+        <v>0.2423115674225332</v>
       </c>
       <c r="C85">
-        <v>-56.73416809487928</v>
+        <v>-57.88823263463954</v>
       </c>
       <c r="D85">
-        <v>19.65783190512073</v>
+        <v>19.46776736536047</v>
       </c>
       <c r="E85">
-        <v>65.31200000000001</v>
+        <v>66.27600000000001</v>
       </c>
       <c r="F85">
-        <v>80.01200000000001</v>
+        <v>80.97600000000001</v>
       </c>
       <c r="G85">
         <v>3.62</v>
@@ -8388,37 +8388,37 @@
         <v>2.27</v>
       </c>
       <c r="M85">
-        <v>18.8668296</v>
+        <v>19.09414080000001</v>
       </c>
       <c r="N85">
-        <v>-16.5968296</v>
+        <v>-16.82414080000001</v>
       </c>
       <c r="O85">
-        <v>-3.319365920000001</v>
+        <v>-3.364828160000001</v>
       </c>
       <c r="P85">
-        <v>-13.27746368</v>
+        <v>-13.45931264</v>
       </c>
       <c r="Q85">
-        <v>-10.04746368</v>
+        <v>-10.22931264</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2906300646529288</v>
+        <v>0.3059319436937369</v>
       </c>
       <c r="T85">
-        <v>4.77219366204528</v>
+        <v>5.070455765923111</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02406339642777078</v>
+        <v>0.02377692742267826</v>
       </c>
       <c r="W85">
-        <v>0.2301258511223317</v>
+        <v>0.2301934005137325</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1203169821388539</v>
+        <v>0.1188846371133913</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2423115674225332</v>
+        <v>0.2442115674225331</v>
       </c>
       <c r="C86">
-        <v>-57.88823263463951</v>
+        <v>-59.03865703758481</v>
       </c>
       <c r="D86">
-        <v>19.46776736536048</v>
+        <v>19.28134296241519</v>
       </c>
       <c r="E86">
-        <v>66.276</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="F86">
-        <v>80.976</v>
+        <v>81.94</v>
       </c>
       <c r="G86">
         <v>3.62</v>
@@ -8470,37 +8470,37 @@
         <v>2.27</v>
       </c>
       <c r="M86">
-        <v>19.0941408</v>
+        <v>19.321452</v>
       </c>
       <c r="N86">
-        <v>-16.8241408</v>
+        <v>-17.051452</v>
       </c>
       <c r="O86">
-        <v>-3.364828160000001</v>
+        <v>-3.4102904</v>
       </c>
       <c r="P86">
-        <v>-13.45931264</v>
+        <v>-13.6411616</v>
       </c>
       <c r="Q86">
-        <v>-10.22931264</v>
+        <v>-10.4111616</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3059319436937367</v>
+        <v>0.3232740732733191</v>
       </c>
       <c r="T86">
-        <v>5.070455765923106</v>
+        <v>5.408486150317981</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02377692742267827</v>
+        <v>0.02349719886476441</v>
       </c>
       <c r="W86">
-        <v>0.2301934005137325</v>
+        <v>0.2302593605076886</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1188846371133914</v>
+        <v>0.117485994323822</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2442115674225331</v>
+        <v>0.2461115674225332</v>
       </c>
       <c r="C87">
-        <v>-59.03865703758481</v>
+        <v>-60.18554488624966</v>
       </c>
       <c r="D87">
-        <v>19.28134296241519</v>
+        <v>19.09845511375035</v>
       </c>
       <c r="E87">
-        <v>67.23999999999999</v>
+        <v>68.20400000000001</v>
       </c>
       <c r="F87">
-        <v>81.94</v>
+        <v>82.90400000000001</v>
       </c>
       <c r="G87">
         <v>3.62</v>
@@ -8552,37 +8552,37 @@
         <v>2.27</v>
       </c>
       <c r="M87">
-        <v>19.321452</v>
+        <v>19.5487632</v>
       </c>
       <c r="N87">
-        <v>-17.051452</v>
+        <v>-17.2787632</v>
       </c>
       <c r="O87">
-        <v>-3.4102904</v>
+        <v>-3.455752640000001</v>
       </c>
       <c r="P87">
-        <v>-13.6411616</v>
+        <v>-13.82301056</v>
       </c>
       <c r="Q87">
-        <v>-10.4111616</v>
+        <v>-10.59301056</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3232740732733191</v>
+        <v>0.3430936499356991</v>
       </c>
       <c r="T87">
-        <v>5.408486150317981</v>
+        <v>5.794806589626408</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02349719886476441</v>
+        <v>0.02322397562215087</v>
       </c>
       <c r="W87">
-        <v>0.2302593605076886</v>
+        <v>0.2303237865482969</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.117485994323822</v>
+        <v>0.1161198781107543</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2461115674225332</v>
+        <v>0.2480115674225332</v>
       </c>
       <c r="C88">
-        <v>-60.18554488624966</v>
+        <v>-61.32899587008136</v>
       </c>
       <c r="D88">
-        <v>19.09845511375035</v>
+        <v>18.91900412991864</v>
       </c>
       <c r="E88">
-        <v>68.20400000000001</v>
+        <v>69.16800000000001</v>
       </c>
       <c r="F88">
-        <v>82.90400000000001</v>
+        <v>83.86800000000001</v>
       </c>
       <c r="G88">
         <v>3.62</v>
@@ -8634,37 +8634,37 @@
         <v>2.27</v>
       </c>
       <c r="M88">
-        <v>19.5487632</v>
+        <v>19.7760744</v>
       </c>
       <c r="N88">
-        <v>-17.2787632</v>
+        <v>-17.5060744</v>
       </c>
       <c r="O88">
-        <v>-3.455752640000001</v>
+        <v>-3.501214880000001</v>
       </c>
       <c r="P88">
-        <v>-13.82301056</v>
+        <v>-14.00485952</v>
       </c>
       <c r="Q88">
-        <v>-10.59301056</v>
+        <v>-10.77485952</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3430936499356991</v>
+        <v>0.3659623922384452</v>
       </c>
       <c r="T88">
-        <v>5.794806589626408</v>
+        <v>6.240560942674593</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02322397562215087</v>
+        <v>0.0229570333736204</v>
       </c>
       <c r="W88">
-        <v>0.2303237865482969</v>
+        <v>0.2303867315305003</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1161198781107543</v>
+        <v>0.1147851668681019</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2480115674225332</v>
+        <v>0.2499115674225331</v>
       </c>
       <c r="C89">
-        <v>-61.32899587008136</v>
+        <v>-62.46910596663671</v>
       </c>
       <c r="D89">
-        <v>18.91900412991864</v>
+        <v>18.7428940333633</v>
       </c>
       <c r="E89">
-        <v>69.16800000000001</v>
+        <v>70.13200000000001</v>
       </c>
       <c r="F89">
-        <v>83.86800000000001</v>
+        <v>84.83200000000001</v>
       </c>
       <c r="G89">
         <v>3.62</v>
@@ -8716,37 +8716,37 @@
         <v>2.27</v>
       </c>
       <c r="M89">
-        <v>19.7760744</v>
+        <v>20.0033856</v>
       </c>
       <c r="N89">
-        <v>-17.5060744</v>
+        <v>-17.7333856</v>
       </c>
       <c r="O89">
-        <v>-3.501214880000001</v>
+        <v>-3.54667712</v>
       </c>
       <c r="P89">
-        <v>-14.00485952</v>
+        <v>-14.18670848</v>
       </c>
       <c r="Q89">
-        <v>-10.77485952</v>
+        <v>-10.95670848</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3659623922384452</v>
+        <v>0.3926425915916489</v>
       </c>
       <c r="T89">
-        <v>6.240560942674593</v>
+        <v>6.760607687897476</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0229570333736204</v>
+        <v>0.02269615799437471</v>
       </c>
       <c r="W89">
-        <v>0.2303867315305003</v>
+        <v>0.2304482459449264</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1147851668681019</v>
+        <v>0.1134807899718735</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2499115674225331</v>
+        <v>0.2518115674225332</v>
       </c>
       <c r="C90">
-        <v>-62.46910596663671</v>
+        <v>-63.60596761275171</v>
       </c>
       <c r="D90">
-        <v>18.7428940333633</v>
+        <v>18.57003238724829</v>
       </c>
       <c r="E90">
-        <v>70.13200000000001</v>
+        <v>71.096</v>
       </c>
       <c r="F90">
-        <v>84.83200000000001</v>
+        <v>85.79600000000001</v>
       </c>
       <c r="G90">
         <v>3.62</v>
@@ -8798,37 +8798,37 @@
         <v>2.27</v>
       </c>
       <c r="M90">
-        <v>20.0033856</v>
+        <v>20.2306968</v>
       </c>
       <c r="N90">
-        <v>-17.7333856</v>
+        <v>-17.9606968</v>
       </c>
       <c r="O90">
-        <v>-3.54667712</v>
+        <v>-3.592139360000001</v>
       </c>
       <c r="P90">
-        <v>-14.18670848</v>
+        <v>-14.36855744</v>
       </c>
       <c r="Q90">
-        <v>-10.95670848</v>
+        <v>-11.13855744</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3926425915916489</v>
+        <v>0.4241737362817989</v>
       </c>
       <c r="T90">
-        <v>6.760607687897476</v>
+        <v>7.375208386797249</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02269615799437471</v>
+        <v>0.02244114498320196</v>
       </c>
       <c r="W90">
-        <v>0.2304482459449264</v>
+        <v>0.230508378012961</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1134807899718735</v>
+        <v>0.1122057249160098</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2518115674225332</v>
+        <v>0.2537115674225331</v>
       </c>
       <c r="C91">
-        <v>-63.60596761275171</v>
+        <v>-64.73966986632603</v>
       </c>
       <c r="D91">
-        <v>18.57003238724829</v>
+        <v>18.40033013367398</v>
       </c>
       <c r="E91">
-        <v>71.096</v>
+        <v>72.06</v>
       </c>
       <c r="F91">
-        <v>85.79600000000001</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="G91">
         <v>3.62</v>
@@ -8880,37 +8880,37 @@
         <v>2.27</v>
       </c>
       <c r="M91">
-        <v>20.2306968</v>
+        <v>20.458008</v>
       </c>
       <c r="N91">
-        <v>-17.9606968</v>
+        <v>-18.188008</v>
       </c>
       <c r="O91">
-        <v>-3.592139360000001</v>
+        <v>-3.637601600000001</v>
       </c>
       <c r="P91">
-        <v>-14.36855744</v>
+        <v>-14.5504064</v>
       </c>
       <c r="Q91">
-        <v>-11.13855744</v>
+        <v>-11.3204064</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4241737362817989</v>
+        <v>0.4620111099099787</v>
       </c>
       <c r="T91">
-        <v>7.375208386797249</v>
+        <v>8.112729225476972</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02244114498320196</v>
+        <v>0.02219179892783305</v>
       </c>
       <c r="W91">
-        <v>0.230508378012961</v>
+        <v>0.230567173812817</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1122057249160098</v>
+        <v>0.1109589946391653</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2537115674225331</v>
+        <v>0.2556115674225332</v>
       </c>
       <c r="C92">
-        <v>-64.73966986632603</v>
+        <v>-65.87029855931688</v>
       </c>
       <c r="D92">
-        <v>18.40033013367398</v>
+        <v>18.23370144068312</v>
       </c>
       <c r="E92">
-        <v>72.06</v>
+        <v>73.024</v>
       </c>
       <c r="F92">
-        <v>86.76000000000001</v>
+        <v>87.724</v>
       </c>
       <c r="G92">
         <v>3.62</v>
@@ -8962,37 +8962,37 @@
         <v>2.27</v>
       </c>
       <c r="M92">
-        <v>20.458008</v>
+        <v>20.6853192</v>
       </c>
       <c r="N92">
-        <v>-18.188008</v>
+        <v>-18.4153192</v>
       </c>
       <c r="O92">
-        <v>-3.637601600000001</v>
+        <v>-3.683063840000001</v>
       </c>
       <c r="P92">
-        <v>-14.5504064</v>
+        <v>-14.73225536</v>
       </c>
       <c r="Q92">
-        <v>-11.3204064</v>
+        <v>-11.50225536</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4620111099099787</v>
+        <v>0.5082567887888653</v>
       </c>
       <c r="T92">
-        <v>8.112729225476972</v>
+        <v>9.014143583863303</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02219179892783305</v>
+        <v>0.02194793300554917</v>
       </c>
       <c r="W92">
-        <v>0.230567173812817</v>
+        <v>0.2306246773972915</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1109589946391653</v>
+        <v>0.1097396650277458</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2556115674225332</v>
+        <v>0.2575115674225332</v>
       </c>
       <c r="C93">
-        <v>-65.87029855931688</v>
+        <v>-66.99793644249478</v>
       </c>
       <c r="D93">
-        <v>18.23370144068312</v>
+        <v>18.07006355750523</v>
       </c>
       <c r="E93">
-        <v>73.024</v>
+        <v>73.988</v>
       </c>
       <c r="F93">
-        <v>87.724</v>
+        <v>88.688</v>
       </c>
       <c r="G93">
         <v>3.62</v>
@@ -9044,37 +9044,37 @@
         <v>2.27</v>
       </c>
       <c r="M93">
-        <v>20.6853192</v>
+        <v>20.9126304</v>
       </c>
       <c r="N93">
-        <v>-18.4153192</v>
+        <v>-18.6426304</v>
       </c>
       <c r="O93">
-        <v>-3.683063840000001</v>
+        <v>-3.72852608</v>
       </c>
       <c r="P93">
-        <v>-14.73225536</v>
+        <v>-14.91410432</v>
       </c>
       <c r="Q93">
-        <v>-11.50225536</v>
+        <v>-11.68410432</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5082567887888653</v>
+        <v>0.5660638873874737</v>
       </c>
       <c r="T93">
-        <v>9.014143583863303</v>
+        <v>10.14091153184622</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02194793300554917</v>
+        <v>0.02170936851635842</v>
       </c>
       <c r="W93">
-        <v>0.2306246773972915</v>
+        <v>0.2306809309038427</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1097396650277458</v>
+        <v>0.108546842581792</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2575115674225332</v>
+        <v>0.2594115674225331</v>
       </c>
       <c r="C94">
-        <v>-66.99793644249478</v>
+        <v>-68.12266332247384</v>
       </c>
       <c r="D94">
-        <v>18.07006355750523</v>
+        <v>17.90933667752617</v>
       </c>
       <c r="E94">
-        <v>73.988</v>
+        <v>74.95200000000001</v>
       </c>
       <c r="F94">
-        <v>88.688</v>
+        <v>89.65200000000002</v>
       </c>
       <c r="G94">
         <v>3.62</v>
@@ -9126,37 +9126,37 @@
         <v>2.27</v>
       </c>
       <c r="M94">
-        <v>20.9126304</v>
+        <v>21.1399416</v>
       </c>
       <c r="N94">
-        <v>-18.6426304</v>
+        <v>-18.8699416</v>
       </c>
       <c r="O94">
-        <v>-3.72852608</v>
+        <v>-3.773988320000001</v>
       </c>
       <c r="P94">
-        <v>-14.91410432</v>
+        <v>-15.09595328</v>
       </c>
       <c r="Q94">
-        <v>-11.68410432</v>
+        <v>-11.86595328</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5660638873874737</v>
+        <v>0.6403872998713985</v>
       </c>
       <c r="T94">
-        <v>10.14091153184622</v>
+        <v>11.58961317925282</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02170936851635842</v>
+        <v>0.02147593444629005</v>
       </c>
       <c r="W94">
-        <v>0.2306809309038427</v>
+        <v>0.2307359746575648</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.108546842581792</v>
+        <v>0.1073796722314502</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2594115674225331</v>
+        <v>0.2613115674225332</v>
       </c>
       <c r="C95">
-        <v>-68.12266332247384</v>
+        <v>-69.24455619149366</v>
       </c>
       <c r="D95">
-        <v>17.90933667752617</v>
+        <v>17.75144380850635</v>
       </c>
       <c r="E95">
-        <v>74.95200000000001</v>
+        <v>75.91600000000001</v>
       </c>
       <c r="F95">
-        <v>89.65200000000002</v>
+        <v>90.61600000000001</v>
       </c>
       <c r="G95">
         <v>3.62</v>
@@ -9208,37 +9208,37 @@
         <v>2.27</v>
       </c>
       <c r="M95">
-        <v>21.1399416</v>
+        <v>21.3672528</v>
       </c>
       <c r="N95">
-        <v>-18.8699416</v>
+        <v>-19.0972528</v>
       </c>
       <c r="O95">
-        <v>-3.773988320000001</v>
+        <v>-3.819450560000001</v>
       </c>
       <c r="P95">
-        <v>-15.09595328</v>
+        <v>-15.27780224</v>
       </c>
       <c r="Q95">
-        <v>-11.86595328</v>
+        <v>-12.04780224</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6403872998713985</v>
+        <v>0.7394851831832985</v>
       </c>
       <c r="T95">
-        <v>11.58961317925282</v>
+        <v>13.52121537579496</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02147593444629005</v>
+        <v>0.02124746705856356</v>
       </c>
       <c r="W95">
-        <v>0.2307359746575648</v>
+        <v>0.2307898472675907</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1073796722314502</v>
+        <v>0.1062373352928178</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2613115674225332</v>
+        <v>0.2632115674225332</v>
       </c>
       <c r="C96">
-        <v>-69.24455619149366</v>
+        <v>-70.36368935039597</v>
       </c>
       <c r="D96">
-        <v>17.75144380850635</v>
+        <v>17.59631064960404</v>
       </c>
       <c r="E96">
-        <v>75.91600000000001</v>
+        <v>76.88000000000001</v>
       </c>
       <c r="F96">
-        <v>90.61600000000001</v>
+        <v>91.58000000000001</v>
       </c>
       <c r="G96">
         <v>3.62</v>
@@ -9290,37 +9290,37 @@
         <v>2.27</v>
       </c>
       <c r="M96">
-        <v>21.3672528</v>
+        <v>21.59456400000001</v>
       </c>
       <c r="N96">
-        <v>-19.0972528</v>
+        <v>-19.32456400000001</v>
       </c>
       <c r="O96">
-        <v>-3.819450560000001</v>
+        <v>-3.864912800000001</v>
       </c>
       <c r="P96">
-        <v>-15.27780224</v>
+        <v>-15.45965120000001</v>
       </c>
       <c r="Q96">
-        <v>-12.04780224</v>
+        <v>-12.2296512</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7394851831832985</v>
+        <v>0.8782222198199585</v>
       </c>
       <c r="T96">
-        <v>13.52121537579496</v>
+        <v>16.22545845095397</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02124746705856356</v>
+        <v>0.02102380951057868</v>
       </c>
       <c r="W96">
-        <v>0.2307898472675907</v>
+        <v>0.2308425857174055</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1062373352928178</v>
+        <v>0.1051190475528934</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2632115674225332</v>
+        <v>0.2651115674225332</v>
       </c>
       <c r="C97">
-        <v>-70.36368935039597</v>
+        <v>-71.480134525209</v>
       </c>
       <c r="D97">
-        <v>17.59631064960404</v>
+        <v>17.44386547479101</v>
       </c>
       <c r="E97">
-        <v>76.88000000000001</v>
+        <v>77.84400000000001</v>
       </c>
       <c r="F97">
-        <v>91.58000000000001</v>
+        <v>92.54400000000001</v>
       </c>
       <c r="G97">
         <v>3.62</v>
@@ -9372,37 +9372,37 @@
         <v>2.27</v>
       </c>
       <c r="M97">
-        <v>21.59456400000001</v>
+        <v>21.8218752</v>
       </c>
       <c r="N97">
-        <v>-19.32456400000001</v>
+        <v>-19.5518752</v>
       </c>
       <c r="O97">
-        <v>-3.864912800000001</v>
+        <v>-3.910375040000001</v>
       </c>
       <c r="P97">
-        <v>-15.45965120000001</v>
+        <v>-15.64150016</v>
       </c>
       <c r="Q97">
-        <v>-12.2296512</v>
+        <v>-12.41150016</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8782222198199585</v>
+        <v>1.086327774774949</v>
       </c>
       <c r="T97">
-        <v>16.22545845095397</v>
+        <v>20.28182306369247</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02102380951057868</v>
+        <v>0.02080481149484348</v>
       </c>
       <c r="W97">
-        <v>0.2308425857174055</v>
+        <v>0.2308942254495159</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1051190475528934</v>
+        <v>0.1040240574742174</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2651115674225331</v>
+        <v>0.2670115674225332</v>
       </c>
       <c r="C98">
-        <v>-71.480134525209</v>
+        <v>-72.59396097772355</v>
       </c>
       <c r="D98">
-        <v>17.44386547479101</v>
+        <v>17.29403902227645</v>
       </c>
       <c r="E98">
-        <v>77.84399999999999</v>
+        <v>78.80800000000001</v>
       </c>
       <c r="F98">
-        <v>92.544</v>
+        <v>93.50800000000001</v>
       </c>
       <c r="G98">
         <v>3.62</v>
@@ -9454,37 +9454,37 @@
         <v>2.27</v>
       </c>
       <c r="M98">
-        <v>21.8218752</v>
+        <v>22.0491864</v>
       </c>
       <c r="N98">
-        <v>-19.5518752</v>
+        <v>-19.7791864</v>
       </c>
       <c r="O98">
-        <v>-3.91037504</v>
+        <v>-3.955837280000001</v>
       </c>
       <c r="P98">
-        <v>-15.64150016</v>
+        <v>-15.82334912</v>
       </c>
       <c r="Q98">
-        <v>-12.41150016</v>
+        <v>-12.59334912</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.086327774774946</v>
+        <v>1.433170366366595</v>
       </c>
       <c r="T98">
-        <v>20.28182306369241</v>
+        <v>27.04243075158988</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02080481149484349</v>
+        <v>0.02059032890211314</v>
       </c>
       <c r="W98">
-        <v>0.2308942254495159</v>
+        <v>0.2309448004448817</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1040240574742174</v>
+        <v>0.1029516445105657</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2670115674225332</v>
+        <v>0.2689115674225331</v>
       </c>
       <c r="C99">
-        <v>-72.59396097772355</v>
+        <v>-73.70523561041929</v>
       </c>
       <c r="D99">
-        <v>17.29403902227645</v>
+        <v>17.14676438958071</v>
       </c>
       <c r="E99">
-        <v>78.80800000000001</v>
+        <v>79.77200000000001</v>
       </c>
       <c r="F99">
-        <v>93.50800000000001</v>
+        <v>94.47200000000001</v>
       </c>
       <c r="G99">
         <v>3.62</v>
@@ -9536,37 +9536,37 @@
         <v>2.27</v>
       </c>
       <c r="M99">
-        <v>22.0491864</v>
+        <v>22.2764976</v>
       </c>
       <c r="N99">
-        <v>-19.7791864</v>
+        <v>-20.0064976</v>
       </c>
       <c r="O99">
-        <v>-3.955837280000001</v>
+        <v>-4.001299520000001</v>
       </c>
       <c r="P99">
-        <v>-15.82334912</v>
+        <v>-16.00519808</v>
       </c>
       <c r="Q99">
-        <v>-12.59334912</v>
+        <v>-12.77519808</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.433170366366595</v>
+        <v>2.126855549549892</v>
       </c>
       <c r="T99">
-        <v>27.04243075158988</v>
+        <v>40.56364612738482</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02059032890211314</v>
+        <v>0.0203802235051528</v>
       </c>
       <c r="W99">
-        <v>0.2309448004448817</v>
+        <v>0.230994343297485</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1029516445105657</v>
+        <v>0.101901117525764</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2689115674225331</v>
+        <v>0.2708115674225332</v>
       </c>
       <c r="C100">
-        <v>-73.70523561041929</v>
+        <v>-74.81402306607498</v>
       </c>
       <c r="D100">
-        <v>17.14676438958071</v>
+        <v>17.00197693392503</v>
       </c>
       <c r="E100">
-        <v>79.77200000000001</v>
+        <v>80.736</v>
       </c>
       <c r="F100">
-        <v>94.47200000000001</v>
+        <v>95.43600000000001</v>
       </c>
       <c r="G100">
         <v>3.62</v>
@@ -9618,37 +9618,37 @@
         <v>2.27</v>
       </c>
       <c r="M100">
-        <v>22.2764976</v>
+        <v>22.5038088</v>
       </c>
       <c r="N100">
-        <v>-20.0064976</v>
+        <v>-20.2338088</v>
       </c>
       <c r="O100">
-        <v>-4.001299520000001</v>
+        <v>-4.046761760000001</v>
       </c>
       <c r="P100">
-        <v>-16.00519808</v>
+        <v>-16.18704704</v>
       </c>
       <c r="Q100">
-        <v>-12.77519808</v>
+        <v>-12.95704704</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.126855549549892</v>
+        <v>4.207911099099784</v>
       </c>
       <c r="T100">
-        <v>40.56364612738482</v>
+        <v>81.12729225476964</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0203802235051528</v>
+        <v>0.02017436266166641</v>
       </c>
       <c r="W100">
-        <v>0.230994343297485</v>
+        <v>0.2310428852843791</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.101901117525764</v>
+        <v>0.1008718133083321</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2708115674225332</v>
-      </c>
-      <c r="C101">
-        <v>-74.81402306607498</v>
-      </c>
-      <c r="D101">
-        <v>17.00197693392503</v>
-      </c>
-      <c r="E101">
-        <v>80.736</v>
-      </c>
-      <c r="F101">
-        <v>95.43600000000001</v>
-      </c>
-      <c r="G101">
-        <v>3.62</v>
-      </c>
-      <c r="H101">
-        <v>81.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.5</v>
-      </c>
-      <c r="K101">
-        <v>3.23</v>
-      </c>
-      <c r="L101">
-        <v>2.27</v>
-      </c>
-      <c r="M101">
-        <v>22.5038088</v>
-      </c>
-      <c r="N101">
-        <v>-20.2338088</v>
-      </c>
-      <c r="O101">
-        <v>-4.046761760000001</v>
-      </c>
-      <c r="P101">
-        <v>-16.18704704</v>
-      </c>
-      <c r="Q101">
-        <v>-12.95704704</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.207911099099784</v>
-      </c>
-      <c r="T101">
-        <v>81.12729225476964</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02017436266166641</v>
-      </c>
-      <c r="W101">
-        <v>0.2310428852843791</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1008718133083321</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
